--- a/research/traditional_assets/database/data/jamaica/jamaica_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,13 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.1087989906736216</v>
+      </c>
+      <c r="C2">
+        <v>159.4742860106466</v>
+      </c>
+      <c r="D2">
+        <v>161.1067760106465</v>
       </c>
       <c r="E2">
-        <v>-0.049</v>
+        <v>1.61849</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.66749</v>
       </c>
       <c r="G2">
         <v>0.035</v>
@@ -1442,43 +1451,45 @@
         <v>-0.1185</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.393194142</v>
       </c>
       <c r="N2">
-        <v>-0.1185</v>
+        <v>-0.511694142</v>
       </c>
       <c r="O2">
-        <v>-0.029625</v>
+        <v>-0.1279235355</v>
       </c>
       <c r="P2">
-        <v>-0.088875</v>
+        <v>-0.3837706064999999</v>
       </c>
       <c r="Q2">
-        <v>0.497125</v>
+        <v>0.2022293935</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.1073366953926925</v>
+      </c>
+      <c r="T2">
+        <v>0.5951068758602817</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-0.07534445922645511</v>
+      </c>
+      <c r="W2">
+        <v>0.2535662234855982</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-0.3013778369058204</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1486,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1087989906736216</v>
+        <v>0.1106989906736216</v>
       </c>
       <c r="C3">
-        <v>159.4742860106466</v>
+        <v>153.0901914649822</v>
       </c>
       <c r="D3">
-        <v>161.1067760106465</v>
+        <v>156.3901714649822</v>
       </c>
       <c r="E3">
-        <v>1.61849</v>
+        <v>3.28598</v>
       </c>
       <c r="F3">
-        <v>1.66749</v>
+        <v>3.33498</v>
       </c>
       <c r="G3">
         <v>0.035</v>
@@ -1522,37 +1533,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M3">
-        <v>0.393194142</v>
+        <v>0.7863882839999999</v>
       </c>
       <c r="N3">
-        <v>-0.511694142</v>
+        <v>-0.9048882839999999</v>
       </c>
       <c r="O3">
-        <v>-0.1279235355</v>
+        <v>-0.226222071</v>
       </c>
       <c r="P3">
-        <v>-0.3837706064999999</v>
+        <v>-0.6786662129999999</v>
       </c>
       <c r="Q3">
-        <v>0.2022293935</v>
+        <v>-0.09266621299999989</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1073366953926925</v>
+        <v>0.1079646208558833</v>
       </c>
       <c r="T3">
-        <v>0.5951068758602817</v>
+        <v>0.601179395001713</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-0.07534445922645511</v>
+        <v>-0.03767222961322755</v>
       </c>
       <c r="W3">
-        <v>0.2535662234855982</v>
+        <v>0.2446831117427991</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1560,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-0.3013778369058204</v>
+        <v>-0.1506889184529101</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1568,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1106989906736216</v>
+        <v>0.1125989906736216</v>
       </c>
       <c r="C4">
-        <v>153.0901914649822</v>
+        <v>146.974410812878</v>
       </c>
       <c r="D4">
-        <v>156.3901714649822</v>
+        <v>151.941880812878</v>
       </c>
       <c r="E4">
-        <v>3.28598</v>
+        <v>4.953469999999999</v>
       </c>
       <c r="F4">
-        <v>3.33498</v>
+        <v>5.00247</v>
       </c>
       <c r="G4">
         <v>0.035</v>
@@ -1604,37 +1615,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M4">
-        <v>0.7863882839999999</v>
+        <v>1.179582426</v>
       </c>
       <c r="N4">
-        <v>-0.9048882839999999</v>
+        <v>-1.298082426</v>
       </c>
       <c r="O4">
-        <v>-0.226222071</v>
+        <v>-0.3245206065</v>
       </c>
       <c r="P4">
-        <v>-0.6786662129999999</v>
+        <v>-0.9735618195000001</v>
       </c>
       <c r="Q4">
-        <v>-0.09266621299999989</v>
+        <v>-0.3875618195000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1079646208558833</v>
+        <v>0.1086054932358408</v>
       </c>
       <c r="T4">
-        <v>0.601179395001713</v>
+        <v>0.6073771207233803</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-0.03767222961322755</v>
+        <v>-0.0251148197421517</v>
       </c>
       <c r="W4">
-        <v>0.2446831117427991</v>
+        <v>0.2417220744951994</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1642,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-0.1506889184529101</v>
+        <v>-0.100459278968607</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1650,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1125989906736216</v>
+        <v>0.1144989906736216</v>
       </c>
       <c r="C5">
-        <v>146.974410812878</v>
+        <v>141.1046818758318</v>
       </c>
       <c r="D5">
-        <v>151.941880812878</v>
+        <v>147.7396418758318</v>
       </c>
       <c r="E5">
-        <v>4.953469999999999</v>
+        <v>6.620959999999999</v>
       </c>
       <c r="F5">
-        <v>5.00247</v>
+        <v>6.66996</v>
       </c>
       <c r="G5">
         <v>0.035</v>
@@ -1686,37 +1697,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M5">
-        <v>1.179582426</v>
+        <v>1.572776568</v>
       </c>
       <c r="N5">
-        <v>-1.298082426</v>
+        <v>-1.691276568</v>
       </c>
       <c r="O5">
-        <v>-0.3245206065</v>
+        <v>-0.422819142</v>
       </c>
       <c r="P5">
-        <v>-0.9735618195000001</v>
+        <v>-1.268457426</v>
       </c>
       <c r="Q5">
-        <v>-0.3875618195000001</v>
+        <v>-0.6824574259999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1086054932358408</v>
+        <v>0.1092597171237142</v>
       </c>
       <c r="T5">
-        <v>0.6073771207233803</v>
+        <v>0.6137039657309155</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-0.0251148197421517</v>
+        <v>-0.01883611480661378</v>
       </c>
       <c r="W5">
-        <v>0.2417220744951994</v>
+        <v>0.2402415558713996</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1724,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-0.100459278968607</v>
+        <v>-0.07534445922645516</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1732,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1144989906736216</v>
+        <v>0.1163989906736216</v>
       </c>
       <c r="C6">
-        <v>141.1046818758318</v>
+        <v>135.4611390047394</v>
       </c>
       <c r="D6">
-        <v>147.7396418758318</v>
+        <v>143.7635890047394</v>
       </c>
       <c r="E6">
-        <v>6.620959999999999</v>
+        <v>8.288450000000001</v>
       </c>
       <c r="F6">
-        <v>6.66996</v>
+        <v>8.33745</v>
       </c>
       <c r="G6">
         <v>0.035</v>
@@ -1768,37 +1779,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M6">
-        <v>1.572776568</v>
+        <v>1.96597071</v>
       </c>
       <c r="N6">
-        <v>-1.691276568</v>
+        <v>-2.08447071</v>
       </c>
       <c r="O6">
-        <v>-0.422819142</v>
+        <v>-0.5211176775</v>
       </c>
       <c r="P6">
-        <v>-1.268457426</v>
+        <v>-1.5633530325</v>
       </c>
       <c r="Q6">
-        <v>-0.6824574259999999</v>
+        <v>-0.9773530325000003</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1092597171237142</v>
+        <v>0.1099277141460691</v>
       </c>
       <c r="T6">
-        <v>0.6137039657309155</v>
+        <v>0.6201640074754514</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-0.01883611480661378</v>
+        <v>-0.01506889184529102</v>
       </c>
       <c r="W6">
-        <v>0.2402415558713996</v>
+        <v>0.2393532446971196</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1806,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-0.07534445922645516</v>
+        <v>-0.06027556738116413</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1814,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1163989906736216</v>
+        <v>0.1182989906736216</v>
       </c>
       <c r="C7">
-        <v>135.4611390047394</v>
+        <v>130.0259990475326</v>
       </c>
       <c r="D7">
-        <v>143.7635890047394</v>
+        <v>139.9959390475326</v>
       </c>
       <c r="E7">
-        <v>8.288450000000001</v>
+        <v>9.955940000000002</v>
       </c>
       <c r="F7">
-        <v>8.33745</v>
+        <v>10.00494</v>
       </c>
       <c r="G7">
         <v>0.035</v>
@@ -1850,37 +1861,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M7">
-        <v>1.96597071</v>
+        <v>2.359164852000001</v>
       </c>
       <c r="N7">
-        <v>-2.08447071</v>
+        <v>-2.477664852000001</v>
       </c>
       <c r="O7">
-        <v>-0.5211176775</v>
+        <v>-0.6194162130000002</v>
       </c>
       <c r="P7">
-        <v>-1.5633530325</v>
+        <v>-1.858248639000001</v>
       </c>
       <c r="Q7">
-        <v>-0.9773530325000003</v>
+        <v>-1.272248639000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1099277141460691</v>
+        <v>0.1106099238710272</v>
       </c>
       <c r="T7">
-        <v>0.6201640074754514</v>
+        <v>0.6267614969166796</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.01506889184529102</v>
+        <v>-0.01255740987107585</v>
       </c>
       <c r="W7">
-        <v>0.2393532446971196</v>
+        <v>0.2387610372475997</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1888,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-0.06027556738116413</v>
+        <v>-0.05022963948430337</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1896,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1182989906736216</v>
+        <v>0.1201989906736216</v>
       </c>
       <c r="C8">
-        <v>130.0259990475326</v>
+        <v>124.783295435332</v>
       </c>
       <c r="D8">
-        <v>139.9959390475326</v>
+        <v>136.420725435332</v>
       </c>
       <c r="E8">
-        <v>9.95594</v>
+        <v>11.62343</v>
       </c>
       <c r="F8">
-        <v>10.00494</v>
+        <v>11.67243</v>
       </c>
       <c r="G8">
         <v>0.035</v>
@@ -1932,37 +1943,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M8">
-        <v>2.359164852</v>
+        <v>2.752358994</v>
       </c>
       <c r="N8">
-        <v>-2.477664852</v>
+        <v>-2.870858994</v>
       </c>
       <c r="O8">
-        <v>-0.619416213</v>
+        <v>-0.7177147484999999</v>
       </c>
       <c r="P8">
-        <v>-1.858248639</v>
+        <v>-2.1531442455</v>
       </c>
       <c r="Q8">
-        <v>-1.272248639</v>
+        <v>-1.5671442455</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1106099238710272</v>
+        <v>0.1113068047728663</v>
       </c>
       <c r="T8">
-        <v>0.6267614969166796</v>
+        <v>0.6335008678512676</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.01255740987107585</v>
+        <v>-0.01076349417520787</v>
       </c>
       <c r="W8">
-        <v>0.2387610372475997</v>
+        <v>0.238338031926514</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1970,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-0.05022963948430337</v>
+        <v>-0.04305397670083155</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1978,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1201989906736216</v>
+        <v>0.1220989906736216</v>
       </c>
       <c r="C9">
-        <v>124.7832954353321</v>
+        <v>119.7186519993726</v>
       </c>
       <c r="D9">
-        <v>136.4207254353321</v>
+        <v>133.0235719993726</v>
       </c>
       <c r="E9">
-        <v>11.62343</v>
+        <v>13.29092</v>
       </c>
       <c r="F9">
-        <v>11.67243</v>
+        <v>13.33992</v>
       </c>
       <c r="G9">
         <v>0.035</v>
@@ -2014,37 +2025,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M9">
-        <v>2.752358994</v>
+        <v>3.145553136</v>
       </c>
       <c r="N9">
-        <v>-2.870858994</v>
+        <v>-3.264053136</v>
       </c>
       <c r="O9">
-        <v>-0.7177147485000001</v>
+        <v>-0.8160132839999999</v>
       </c>
       <c r="P9">
-        <v>-2.1531442455</v>
+        <v>-2.448039852</v>
       </c>
       <c r="Q9">
-        <v>-1.5671442455</v>
+        <v>-1.862039852</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1113068047728663</v>
+        <v>0.1120188352595278</v>
       </c>
       <c r="T9">
-        <v>0.6335008678512676</v>
+        <v>0.640386746849651</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.01076349417520787</v>
+        <v>-0.009418057403306888</v>
       </c>
       <c r="W9">
-        <v>0.238338031926514</v>
+        <v>0.2380207779356998</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2052,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-0.04305397670083155</v>
+        <v>-0.03767222961322747</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2060,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1220989906736216</v>
+        <v>0.1239989906736216</v>
       </c>
       <c r="C10">
-        <v>119.7186519993726</v>
+        <v>114.8190897613346</v>
       </c>
       <c r="D10">
-        <v>133.0235719993726</v>
+        <v>129.7914997613346</v>
       </c>
       <c r="E10">
-        <v>13.29092</v>
+        <v>14.95841</v>
       </c>
       <c r="F10">
-        <v>13.33992</v>
+        <v>15.00741</v>
       </c>
       <c r="G10">
         <v>0.035</v>
@@ -2096,37 +2107,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M10">
-        <v>3.145553136</v>
+        <v>3.538747278</v>
       </c>
       <c r="N10">
-        <v>-3.264053136</v>
+        <v>-3.657247278</v>
       </c>
       <c r="O10">
-        <v>-0.8160132839999999</v>
+        <v>-0.9143118195</v>
       </c>
       <c r="P10">
-        <v>-2.448039852</v>
+        <v>-2.7429354585</v>
       </c>
       <c r="Q10">
-        <v>-1.862039852</v>
+        <v>-2.1569354585</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1120188352595278</v>
+        <v>0.1127465147678743</v>
       </c>
       <c r="T10">
-        <v>0.640386746849651</v>
+        <v>0.6474239638479987</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.009418057403306888</v>
+        <v>-0.008371606580717235</v>
       </c>
       <c r="W10">
-        <v>0.2380207779356998</v>
+        <v>0.2377740248317332</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2134,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-0.03767222961322747</v>
+        <v>-0.03348642632286891</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2142,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1239989906736216</v>
+        <v>0.1258989906736216</v>
       </c>
       <c r="C11">
-        <v>114.8190897613346</v>
+        <v>110.0728612220268</v>
       </c>
       <c r="D11">
-        <v>129.7914997613346</v>
+        <v>126.7127612220268</v>
       </c>
       <c r="E11">
-        <v>14.95841</v>
+        <v>16.6259</v>
       </c>
       <c r="F11">
-        <v>15.00741</v>
+        <v>16.6749</v>
       </c>
       <c r="G11">
         <v>0.035</v>
@@ -2178,37 +2189,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M11">
-        <v>3.538747278</v>
+        <v>3.931941419999999</v>
       </c>
       <c r="N11">
-        <v>-3.657247278</v>
+        <v>-4.050441419999999</v>
       </c>
       <c r="O11">
-        <v>-0.9143118195</v>
+        <v>-1.012610355</v>
       </c>
       <c r="P11">
-        <v>-2.7429354585</v>
+        <v>-3.037831065</v>
       </c>
       <c r="Q11">
-        <v>-2.1569354585</v>
+        <v>-2.451831065</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1127465147678743</v>
+        <v>0.1134903649319618</v>
       </c>
       <c r="T11">
-        <v>0.6474239638479987</v>
+        <v>0.6546175634463098</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.008371606580717235</v>
+        <v>-0.007534445922645512</v>
       </c>
       <c r="W11">
-        <v>0.2377740248317332</v>
+        <v>0.2375766223485598</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2216,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-0.03348642632286891</v>
+        <v>-0.03013778369058207</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2224,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1258989906736216</v>
+        <v>0.1277989906736216</v>
       </c>
       <c r="C12">
-        <v>110.0728612220268</v>
+        <v>105.4693076882679</v>
       </c>
       <c r="D12">
-        <v>126.7127612220268</v>
+        <v>123.7766976882679</v>
       </c>
       <c r="E12">
-        <v>16.6259</v>
+        <v>18.29339</v>
       </c>
       <c r="F12">
-        <v>16.6749</v>
+        <v>18.34239</v>
       </c>
       <c r="G12">
         <v>0.035</v>
@@ -2260,37 +2271,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M12">
-        <v>3.93194142</v>
+        <v>4.325135562</v>
       </c>
       <c r="N12">
-        <v>-4.05044142</v>
+        <v>-4.443635562</v>
       </c>
       <c r="O12">
-        <v>-1.012610355</v>
+        <v>-1.1109088905</v>
       </c>
       <c r="P12">
-        <v>-3.037831065</v>
+        <v>-3.3327266715</v>
       </c>
       <c r="Q12">
-        <v>-2.451831065</v>
+        <v>-2.7467266715</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1134903649319618</v>
+        <v>0.1142509308300737</v>
       </c>
       <c r="T12">
-        <v>0.6546175634463098</v>
+        <v>0.6619728169681786</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.00753444592264551</v>
+        <v>-0.0068494962933141</v>
       </c>
       <c r="W12">
-        <v>0.2375766223485598</v>
+        <v>0.2374151112259635</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2298,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.03013778369058207</v>
+        <v>-0.02739798517325642</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2306,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1277989906736216</v>
+        <v>0.1296989906736216</v>
       </c>
       <c r="C13">
-        <v>105.4693076882679</v>
+        <v>100.9987359858602</v>
       </c>
       <c r="D13">
-        <v>123.7766976882679</v>
+        <v>120.9736159858602</v>
       </c>
       <c r="E13">
-        <v>18.29339</v>
+        <v>19.96088</v>
       </c>
       <c r="F13">
-        <v>18.34239</v>
+        <v>20.00988</v>
       </c>
       <c r="G13">
         <v>0.035</v>
@@ -2342,37 +2353,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M13">
-        <v>4.325135562</v>
+        <v>4.718329704</v>
       </c>
       <c r="N13">
-        <v>-4.443635562</v>
+        <v>-4.836829704</v>
       </c>
       <c r="O13">
-        <v>-1.1109088905</v>
+        <v>-1.209207426</v>
       </c>
       <c r="P13">
-        <v>-3.3327266715</v>
+        <v>-3.627622278</v>
       </c>
       <c r="Q13">
-        <v>-2.7467266715</v>
+        <v>-3.041622278000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1142509308300737</v>
+        <v>0.1150287823167791</v>
       </c>
       <c r="T13">
-        <v>0.6619728169681786</v>
+        <v>0.6694952353428169</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.0068494962933141</v>
+        <v>-0.006278704935537925</v>
       </c>
       <c r="W13">
-        <v>0.2374151112259635</v>
+        <v>0.2372805186237999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2380,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.02739798517325642</v>
+        <v>-0.02511481974215179</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2388,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1296989906736216</v>
+        <v>0.1315989906736216</v>
       </c>
       <c r="C14">
-        <v>100.9987359858602</v>
+        <v>96.65231155354874</v>
       </c>
       <c r="D14">
-        <v>120.9736159858602</v>
+        <v>118.2946815535487</v>
       </c>
       <c r="E14">
-        <v>19.96088</v>
+        <v>21.62837</v>
       </c>
       <c r="F14">
-        <v>20.00988</v>
+        <v>21.67737</v>
       </c>
       <c r="G14">
         <v>0.035</v>
@@ -2424,37 +2435,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M14">
-        <v>4.718329704</v>
+        <v>5.111523846</v>
       </c>
       <c r="N14">
-        <v>-4.836829704</v>
+        <v>-5.230023846</v>
       </c>
       <c r="O14">
-        <v>-1.209207426</v>
+        <v>-1.3075059615</v>
       </c>
       <c r="P14">
-        <v>-3.627622278</v>
+        <v>-3.9225178845</v>
       </c>
       <c r="Q14">
-        <v>-3.041622278000001</v>
+        <v>-3.3365178845</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1150287823167791</v>
+        <v>0.115824515446857</v>
       </c>
       <c r="T14">
-        <v>0.6694952353428169</v>
+        <v>0.6771905828754929</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.006278704935537925</v>
+        <v>-0.005795727632804239</v>
       </c>
       <c r="W14">
-        <v>0.2372805186237999</v>
+        <v>0.2371666325758152</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2462,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.02511481974215179</v>
+        <v>-0.0231829105312169</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2470,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1315989906736216</v>
+        <v>0.1334989906736216</v>
       </c>
       <c r="C15">
-        <v>96.65231155354874</v>
+        <v>92.42196543370802</v>
       </c>
       <c r="D15">
-        <v>118.2946815535487</v>
+        <v>115.731825433708</v>
       </c>
       <c r="E15">
-        <v>21.62837</v>
+        <v>23.29586</v>
       </c>
       <c r="F15">
-        <v>21.67737</v>
+        <v>23.34486</v>
       </c>
       <c r="G15">
         <v>0.035</v>
@@ -2506,37 +2517,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M15">
-        <v>5.111523846</v>
+        <v>5.504717988</v>
       </c>
       <c r="N15">
-        <v>-5.230023846</v>
+        <v>-5.623217988</v>
       </c>
       <c r="O15">
-        <v>-1.3075059615</v>
+        <v>-1.405804497</v>
       </c>
       <c r="P15">
-        <v>-3.9225178845</v>
+        <v>-4.217413491</v>
       </c>
       <c r="Q15">
-        <v>-3.3365178845</v>
+        <v>-3.631413491</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.115824515446857</v>
+        <v>0.1166387539985647</v>
       </c>
       <c r="T15">
-        <v>0.6771905828754929</v>
+        <v>0.6850648919786964</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.005795727632804239</v>
+        <v>-0.005381747087603935</v>
       </c>
       <c r="W15">
-        <v>0.2371666325758152</v>
+        <v>0.237069015963257</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2544,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.0231829105312169</v>
+        <v>-0.02152698835041567</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2552,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1334989906736216</v>
+        <v>0.1353989906736216</v>
       </c>
       <c r="C16">
-        <v>92.42196543370802</v>
+        <v>88.30031309693537</v>
       </c>
       <c r="D16">
-        <v>115.731825433708</v>
+        <v>113.2776630969354</v>
       </c>
       <c r="E16">
-        <v>23.29586</v>
+        <v>24.96335</v>
       </c>
       <c r="F16">
-        <v>23.34486</v>
+        <v>25.01235</v>
       </c>
       <c r="G16">
         <v>0.035</v>
@@ -2588,37 +2599,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M16">
-        <v>5.504717988</v>
+        <v>5.897912130000001</v>
       </c>
       <c r="N16">
-        <v>-5.623217988</v>
+        <v>-6.016412130000001</v>
       </c>
       <c r="O16">
-        <v>-1.405804497</v>
+        <v>-1.5041030325</v>
       </c>
       <c r="P16">
-        <v>-4.217413491</v>
+        <v>-4.512309097500001</v>
       </c>
       <c r="Q16">
-        <v>-3.631413491</v>
+        <v>-3.926309097500001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1166387539985647</v>
+        <v>0.1174721511044301</v>
       </c>
       <c r="T16">
-        <v>0.6850648919786964</v>
+        <v>0.6931244789431515</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.005381747087603935</v>
+        <v>-0.00502296394843034</v>
       </c>
       <c r="W16">
-        <v>0.237069015963257</v>
+        <v>0.2369844148990399</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2626,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.02152698835041567</v>
+        <v>-0.0200918557937213</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2634,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1353989906736216</v>
+        <v>0.1372989906736216</v>
       </c>
       <c r="C17">
-        <v>88.30031309693537</v>
+        <v>84.28058338041329</v>
       </c>
       <c r="D17">
-        <v>113.2776630969354</v>
+        <v>110.9254233804133</v>
       </c>
       <c r="E17">
-        <v>24.96335</v>
+        <v>26.63084</v>
       </c>
       <c r="F17">
-        <v>25.01235</v>
+        <v>26.67984</v>
       </c>
       <c r="G17">
         <v>0.035</v>
@@ -2670,37 +2681,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M17">
-        <v>5.89791213</v>
+        <v>6.291106271999999</v>
       </c>
       <c r="N17">
-        <v>-6.01641213</v>
+        <v>-6.409606272</v>
       </c>
       <c r="O17">
-        <v>-1.5041030325</v>
+        <v>-1.602401568</v>
       </c>
       <c r="P17">
-        <v>-4.5123090975</v>
+        <v>-4.807204704</v>
       </c>
       <c r="Q17">
-        <v>-3.9263090975</v>
+        <v>-4.221204704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1174721511044301</v>
+        <v>0.1183253909985305</v>
       </c>
       <c r="T17">
-        <v>0.6931244789431515</v>
+        <v>0.701375960835332</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.00502296394843034</v>
+        <v>-0.004709028701653444</v>
       </c>
       <c r="W17">
-        <v>0.2369844148990399</v>
+        <v>0.2369103889678499</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2708,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.0200918557937213</v>
+        <v>-0.01883611480661385</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2716,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1372989906736216</v>
+        <v>0.1391989906736216</v>
       </c>
       <c r="C18">
-        <v>84.28058338041329</v>
+        <v>80.35655609984168</v>
       </c>
       <c r="D18">
-        <v>110.9254233804133</v>
+        <v>108.6688860998417</v>
       </c>
       <c r="E18">
-        <v>26.63084</v>
+        <v>28.29833</v>
       </c>
       <c r="F18">
-        <v>26.67984</v>
+        <v>28.34733</v>
       </c>
       <c r="G18">
         <v>0.035</v>
@@ -2752,37 +2763,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M18">
-        <v>6.291106271999999</v>
+        <v>6.684300414</v>
       </c>
       <c r="N18">
-        <v>-6.409606272</v>
+        <v>-6.802800414</v>
       </c>
       <c r="O18">
-        <v>-1.602401568</v>
+        <v>-1.7007001035</v>
       </c>
       <c r="P18">
-        <v>-4.807204704</v>
+        <v>-5.1021003105</v>
       </c>
       <c r="Q18">
-        <v>-4.221204704</v>
+        <v>-4.5161003105</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1183253909985305</v>
+        <v>0.119199190890079</v>
       </c>
       <c r="T18">
-        <v>0.701375960835332</v>
+        <v>0.7098262736164807</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.004709028701653444</v>
+        <v>-0.004432027013320889</v>
       </c>
       <c r="W18">
-        <v>0.2369103889678499</v>
+        <v>0.2368450719697411</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2790,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.01883611480661385</v>
+        <v>-0.01772810805328362</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2798,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1391989906736216</v>
+        <v>0.1410989906736216</v>
       </c>
       <c r="C19">
-        <v>80.35655609984168</v>
+        <v>76.52250712445006</v>
       </c>
       <c r="D19">
-        <v>108.6688860998417</v>
+        <v>106.5023271244501</v>
       </c>
       <c r="E19">
-        <v>28.29833</v>
+        <v>29.96582</v>
       </c>
       <c r="F19">
-        <v>28.34733</v>
+        <v>30.01482</v>
       </c>
       <c r="G19">
         <v>0.035</v>
@@ -2834,37 +2845,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M19">
-        <v>6.684300414</v>
+        <v>7.077494556000001</v>
       </c>
       <c r="N19">
-        <v>-6.802800414</v>
+        <v>-7.195994556000001</v>
       </c>
       <c r="O19">
-        <v>-1.7007001035</v>
+        <v>-1.798998639</v>
       </c>
       <c r="P19">
-        <v>-5.1021003105</v>
+        <v>-5.396995917000001</v>
       </c>
       <c r="Q19">
-        <v>-4.5161003105</v>
+        <v>-4.810995917000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.119199190890079</v>
+        <v>0.1200943029741044</v>
       </c>
       <c r="T19">
-        <v>0.7098262736164807</v>
+        <v>0.7184826915874133</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.004432027013320889</v>
+        <v>-0.004185803290358616</v>
       </c>
       <c r="W19">
-        <v>0.2368450719697411</v>
+        <v>0.2367870124158666</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2872,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.01772810805328362</v>
+        <v>-0.01674321316143446</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2880,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1410989906736216</v>
+        <v>0.1429989906736216</v>
       </c>
       <c r="C20">
-        <v>76.52250712445006</v>
+        <v>72.77315989389578</v>
       </c>
       <c r="D20">
-        <v>106.5023271244501</v>
+        <v>104.4204698938958</v>
       </c>
       <c r="E20">
-        <v>29.96582</v>
+        <v>31.63331</v>
       </c>
       <c r="F20">
-        <v>30.01482</v>
+        <v>31.68231</v>
       </c>
       <c r="G20">
         <v>0.035</v>
@@ -2916,37 +2927,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M20">
-        <v>7.077494556</v>
+        <v>7.470688698000001</v>
       </c>
       <c r="N20">
-        <v>-7.195994556</v>
+        <v>-7.589188698000001</v>
       </c>
       <c r="O20">
-        <v>-1.798998639</v>
+        <v>-1.8972971745</v>
       </c>
       <c r="P20">
-        <v>-5.396995917</v>
+        <v>-5.691891523500001</v>
       </c>
       <c r="Q20">
-        <v>-4.810995917</v>
+        <v>-5.1058915235</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1200943029741044</v>
+        <v>0.1210115165910687</v>
       </c>
       <c r="T20">
-        <v>0.7184826915874133</v>
+        <v>0.7273528482736775</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.004185803290358617</v>
+        <v>-0.003965497854023952</v>
       </c>
       <c r="W20">
-        <v>0.2367870124158666</v>
+        <v>0.2367350643939789</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2954,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.01674321316143446</v>
+        <v>-0.01586199141609579</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2962,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1429989906736216</v>
+        <v>0.1448989906736216</v>
       </c>
       <c r="C21">
-        <v>72.77315989389578</v>
+        <v>69.10364251248862</v>
       </c>
       <c r="D21">
-        <v>104.4204698938958</v>
+        <v>102.4184425124886</v>
       </c>
       <c r="E21">
-        <v>31.63331</v>
+        <v>33.3008</v>
       </c>
       <c r="F21">
-        <v>31.68231</v>
+        <v>33.3498</v>
       </c>
       <c r="G21">
         <v>0.035</v>
@@ -2998,37 +3009,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M21">
-        <v>7.470688698000001</v>
+        <v>7.86388284</v>
       </c>
       <c r="N21">
-        <v>-7.589188698000001</v>
+        <v>-7.982382840000001</v>
       </c>
       <c r="O21">
-        <v>-1.8972971745</v>
+        <v>-1.99559571</v>
       </c>
       <c r="P21">
-        <v>-5.691891523500001</v>
+        <v>-5.986787130000001</v>
       </c>
       <c r="Q21">
-        <v>-5.1058915235</v>
+        <v>-5.40078713</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1210115165910687</v>
+        <v>0.121951660548457</v>
       </c>
       <c r="T21">
-        <v>0.7273528482736775</v>
+        <v>0.7364447588770986</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.003965497854023952</v>
+        <v>-0.003767222961322755</v>
       </c>
       <c r="W21">
-        <v>0.2367350643939789</v>
+        <v>0.2366883111742799</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3036,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.01586199141609579</v>
+        <v>-0.01506889184529103</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3044,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1448989906736216</v>
+        <v>0.1467989906736216</v>
       </c>
       <c r="C22">
-        <v>69.10364251248862</v>
+        <v>65.50944968629344</v>
       </c>
       <c r="D22">
-        <v>102.4184425124886</v>
+        <v>100.4917396862934</v>
       </c>
       <c r="E22">
-        <v>33.3008</v>
+        <v>34.96829</v>
       </c>
       <c r="F22">
-        <v>33.3498</v>
+        <v>35.01729</v>
       </c>
       <c r="G22">
         <v>0.035</v>
@@ -3080,37 +3091,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M22">
-        <v>7.86388284</v>
+        <v>8.257076982000001</v>
       </c>
       <c r="N22">
-        <v>-7.982382840000001</v>
+        <v>-8.375576982</v>
       </c>
       <c r="O22">
-        <v>-1.99559571</v>
+        <v>-2.0938942455</v>
       </c>
       <c r="P22">
-        <v>-5.986787130000001</v>
+        <v>-6.281682736500001</v>
       </c>
       <c r="Q22">
-        <v>-5.40078713</v>
+        <v>-5.6956827365</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.121951660548457</v>
+        <v>0.1229156056186906</v>
       </c>
       <c r="T22">
-        <v>0.7364447588770986</v>
+        <v>0.745766844432505</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.003767222961322755</v>
+        <v>-0.003587831391735957</v>
       </c>
       <c r="W22">
-        <v>0.2366883111742799</v>
+        <v>0.2366460106421713</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3118,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.01506889184529103</v>
+        <v>-0.01435132556694363</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3126,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1467989906736216</v>
+        <v>0.1486989906736216</v>
       </c>
       <c r="C23">
-        <v>65.50944968629344</v>
+        <v>61.98640887715511</v>
       </c>
       <c r="D23">
-        <v>100.4917396862934</v>
+        <v>98.63618887715511</v>
       </c>
       <c r="E23">
-        <v>34.96829</v>
+        <v>36.63578</v>
       </c>
       <c r="F23">
-        <v>35.01729</v>
+        <v>36.68478</v>
       </c>
       <c r="G23">
         <v>0.035</v>
@@ -3162,37 +3173,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M23">
-        <v>8.257076981999999</v>
+        <v>8.650271124</v>
       </c>
       <c r="N23">
-        <v>-8.375576981999998</v>
+        <v>-8.768771123999999</v>
       </c>
       <c r="O23">
-        <v>-2.0938942455</v>
+        <v>-2.192192781</v>
       </c>
       <c r="P23">
-        <v>-6.281682736499999</v>
+        <v>-6.576578343</v>
       </c>
       <c r="Q23">
-        <v>-5.695682736499998</v>
+        <v>-5.990578342999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1229156056186906</v>
+        <v>0.1239042672291867</v>
       </c>
       <c r="T23">
-        <v>0.745766844432505</v>
+        <v>0.7553279578226652</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.003587831391735958</v>
+        <v>-0.00342474814665705</v>
       </c>
       <c r="W23">
-        <v>0.2366460106421713</v>
+        <v>0.2366075556129817</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3200,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.01435132556694363</v>
+        <v>-0.01369899258662821</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3208,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1486989906736216</v>
+        <v>0.1505989906736216</v>
       </c>
       <c r="C24">
-        <v>61.98640887715511</v>
+        <v>58.53065013847758</v>
       </c>
       <c r="D24">
-        <v>98.63618887715511</v>
+        <v>96.84792013847758</v>
       </c>
       <c r="E24">
-        <v>36.63578</v>
+        <v>38.30327</v>
       </c>
       <c r="F24">
-        <v>36.68478</v>
+        <v>38.35227</v>
       </c>
       <c r="G24">
         <v>0.035</v>
@@ -3244,37 +3255,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M24">
-        <v>8.650271124</v>
+        <v>9.043465266</v>
       </c>
       <c r="N24">
-        <v>-8.768771123999999</v>
+        <v>-9.161965265999999</v>
       </c>
       <c r="O24">
-        <v>-2.192192781</v>
+        <v>-2.2904913165</v>
       </c>
       <c r="P24">
-        <v>-6.576578343</v>
+        <v>-6.871473949499999</v>
       </c>
       <c r="Q24">
-        <v>-5.990578342999999</v>
+        <v>-6.285473949499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1239042672291867</v>
+        <v>0.1249186083620333</v>
       </c>
       <c r="T24">
-        <v>0.7553279578226652</v>
+        <v>0.7651374118203621</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.00342474814665705</v>
+        <v>-0.003275846053324135</v>
       </c>
       <c r="W24">
-        <v>0.2366075556129817</v>
+        <v>0.2365724444993739</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3282,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.01369899258662821</v>
+        <v>-0.01310338421329638</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3290,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1505989906736216</v>
+        <v>0.1524989906736216</v>
       </c>
       <c r="C25">
-        <v>58.53065013847758</v>
+        <v>55.13857917382747</v>
       </c>
       <c r="D25">
-        <v>96.84792013847758</v>
+        <v>95.12333917382747</v>
       </c>
       <c r="E25">
-        <v>38.30327</v>
+        <v>39.97076000000001</v>
       </c>
       <c r="F25">
-        <v>38.35227</v>
+        <v>40.01976000000001</v>
       </c>
       <c r="G25">
         <v>0.035</v>
@@ -3326,37 +3337,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M25">
-        <v>9.043465266</v>
+        <v>9.436659408000002</v>
       </c>
       <c r="N25">
-        <v>-9.161965265999999</v>
+        <v>-9.555159408000002</v>
       </c>
       <c r="O25">
-        <v>-2.2904913165</v>
+        <v>-2.388789852</v>
       </c>
       <c r="P25">
-        <v>-6.871473949499999</v>
+        <v>-7.166369556000001</v>
       </c>
       <c r="Q25">
-        <v>-6.285473949499999</v>
+        <v>-6.580369556000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1249186083620333</v>
+        <v>0.1259596426825863</v>
       </c>
       <c r="T25">
-        <v>0.7651374118203621</v>
+        <v>0.7752050093443144</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.003275846053324135</v>
+        <v>-0.003139352467768962</v>
       </c>
       <c r="W25">
-        <v>0.2365724444993739</v>
+        <v>0.2365402593118999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3364,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.01310338421329638</v>
+        <v>-0.01255740987107568</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3372,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1524989906736216</v>
+        <v>0.1543989906736216</v>
       </c>
       <c r="C26">
-        <v>55.13857917382747</v>
+        <v>51.80685322366617</v>
       </c>
       <c r="D26">
-        <v>95.12333917382747</v>
+        <v>93.45910322366618</v>
       </c>
       <c r="E26">
-        <v>39.97076</v>
+        <v>41.63825</v>
       </c>
       <c r="F26">
-        <v>40.01976</v>
+        <v>41.68725</v>
       </c>
       <c r="G26">
         <v>0.035</v>
@@ -3408,37 +3419,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M26">
-        <v>9.436659408000001</v>
+        <v>9.829853549999999</v>
       </c>
       <c r="N26">
-        <v>-9.555159408</v>
+        <v>-9.948353549999998</v>
       </c>
       <c r="O26">
-        <v>-2.388789852</v>
+        <v>-2.4870883875</v>
       </c>
       <c r="P26">
-        <v>-7.166369555999999</v>
+        <v>-7.461265162499998</v>
       </c>
       <c r="Q26">
-        <v>-6.580369555999999</v>
+        <v>-6.875265162499998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1259596426825863</v>
+        <v>0.1270284379183541</v>
       </c>
       <c r="T26">
-        <v>0.7752050093443144</v>
+        <v>0.7855410761355718</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.003139352467768963</v>
+        <v>-0.003013778369058205</v>
       </c>
       <c r="W26">
-        <v>0.2365402593118999</v>
+        <v>0.2365106489394239</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3446,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.01255740987107568</v>
+        <v>-0.01205511347623278</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3454,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1543989906736216</v>
+        <v>0.1562989906736216</v>
       </c>
       <c r="C27">
-        <v>51.80685322366617</v>
+        <v>48.53235943980849</v>
       </c>
       <c r="D27">
-        <v>93.45910322366618</v>
+        <v>91.8520994398085</v>
       </c>
       <c r="E27">
-        <v>41.63825</v>
+        <v>43.30574</v>
       </c>
       <c r="F27">
-        <v>41.68725</v>
+        <v>43.35474</v>
       </c>
       <c r="G27">
         <v>0.035</v>
@@ -3490,37 +3501,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M27">
-        <v>9.829853549999999</v>
+        <v>10.223047692</v>
       </c>
       <c r="N27">
-        <v>-9.948353549999998</v>
+        <v>-10.341547692</v>
       </c>
       <c r="O27">
-        <v>-2.4870883875</v>
+        <v>-2.585386923</v>
       </c>
       <c r="P27">
-        <v>-7.461265162499998</v>
+        <v>-7.756160768999999</v>
       </c>
       <c r="Q27">
-        <v>-6.875265162499998</v>
+        <v>-7.170160768999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1270284379183541</v>
+        <v>0.1281261195118454</v>
       </c>
       <c r="T27">
-        <v>0.7855410761355718</v>
+        <v>0.7961564960833498</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.003013778369058205</v>
+        <v>-0.00289786381640212</v>
       </c>
       <c r="W27">
-        <v>0.2365106489394239</v>
+        <v>0.2364833162879076</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3528,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.01205511347623278</v>
+        <v>-0.01159145526560845</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3536,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1562989906736216</v>
+        <v>0.1581989906736216</v>
       </c>
       <c r="C28">
-        <v>48.53235943980849</v>
+        <v>45.31219545323868</v>
       </c>
       <c r="D28">
-        <v>91.8520994398085</v>
+        <v>90.29942545323868</v>
       </c>
       <c r="E28">
-        <v>43.30574</v>
+        <v>44.97323</v>
       </c>
       <c r="F28">
-        <v>43.35474</v>
+        <v>45.02223</v>
       </c>
       <c r="G28">
         <v>0.035</v>
@@ -3572,37 +3583,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M28">
-        <v>10.223047692</v>
+        <v>10.616241834</v>
       </c>
       <c r="N28">
-        <v>-10.341547692</v>
+        <v>-10.734741834</v>
       </c>
       <c r="O28">
-        <v>-2.585386923</v>
+        <v>-2.6836854585</v>
       </c>
       <c r="P28">
-        <v>-7.756160768999999</v>
+        <v>-8.0510563755</v>
       </c>
       <c r="Q28">
-        <v>-7.170160768999999</v>
+        <v>-7.4650563755</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1281261195118454</v>
+        <v>0.1292538745736515</v>
       </c>
       <c r="T28">
-        <v>0.7961564960833498</v>
+        <v>0.8070627494543546</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.00289786381640212</v>
+        <v>-0.002790535526905745</v>
       </c>
       <c r="W28">
-        <v>0.2364833162879076</v>
+        <v>0.2364580082772444</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3610,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.01159145526560845</v>
+        <v>-0.0111621421076229</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3618,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1581989906736216</v>
+        <v>0.1600989906736216</v>
       </c>
       <c r="C29">
-        <v>45.31219545323868</v>
+        <v>42.14365188006175</v>
       </c>
       <c r="D29">
-        <v>90.29942545323868</v>
+        <v>88.79837188006175</v>
       </c>
       <c r="E29">
-        <v>44.97323</v>
+        <v>46.64072</v>
       </c>
       <c r="F29">
-        <v>45.02223</v>
+        <v>46.68972</v>
       </c>
       <c r="G29">
         <v>0.035</v>
@@ -3654,37 +3665,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M29">
-        <v>10.616241834</v>
+        <v>11.009435976</v>
       </c>
       <c r="N29">
-        <v>-10.734741834</v>
+        <v>-11.127935976</v>
       </c>
       <c r="O29">
-        <v>-2.6836854585</v>
+        <v>-2.781983994</v>
       </c>
       <c r="P29">
-        <v>-8.0510563755</v>
+        <v>-8.345951981999999</v>
       </c>
       <c r="Q29">
-        <v>-7.4650563755</v>
+        <v>-7.759951981999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1292538745736515</v>
+        <v>0.1304129561649522</v>
       </c>
       <c r="T29">
-        <v>0.8070627494543546</v>
+        <v>0.8182719543078874</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.002790535526905745</v>
+        <v>-0.002690873543801968</v>
       </c>
       <c r="W29">
-        <v>0.2364580082772444</v>
+        <v>0.2364345079816285</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3692,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.0111621421076229</v>
+        <v>-0.01076349417520772</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3700,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1600989906736216</v>
+        <v>0.1619989906736216</v>
       </c>
       <c r="C30">
-        <v>42.14365188006175</v>
+        <v>39.02419654375338</v>
       </c>
       <c r="D30">
-        <v>88.79837188006175</v>
+        <v>87.34640654375339</v>
       </c>
       <c r="E30">
-        <v>46.64072</v>
+        <v>48.30821</v>
       </c>
       <c r="F30">
-        <v>46.68972</v>
+        <v>48.35721</v>
       </c>
       <c r="G30">
         <v>0.035</v>
@@ -3736,37 +3747,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M30">
-        <v>11.009435976</v>
+        <v>11.402630118</v>
       </c>
       <c r="N30">
-        <v>-11.127935976</v>
+        <v>-11.521130118</v>
       </c>
       <c r="O30">
-        <v>-2.781983994</v>
+        <v>-2.8802825295</v>
       </c>
       <c r="P30">
-        <v>-8.345951981999999</v>
+        <v>-8.6408475885</v>
       </c>
       <c r="Q30">
-        <v>-7.759951981999999</v>
+        <v>-8.054847588499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1304129561649522</v>
+        <v>0.1316046879419234</v>
       </c>
       <c r="T30">
-        <v>0.8182719543078874</v>
+        <v>0.8297969114108154</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.002690873543801968</v>
+        <v>-0.002598084800912245</v>
       </c>
       <c r="W30">
-        <v>0.2364345079816285</v>
+        <v>0.2364126283960551</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3774,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.01076349417520772</v>
+        <v>-0.0103923392036489</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3782,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1619989906736216</v>
+        <v>0.1638989906736216</v>
       </c>
       <c r="C31">
-        <v>39.0241965437534</v>
+        <v>35.95146022042307</v>
       </c>
       <c r="D31">
-        <v>87.3464065437534</v>
+        <v>85.94116022042307</v>
       </c>
       <c r="E31">
-        <v>48.30821</v>
+        <v>49.9757</v>
       </c>
       <c r="F31">
-        <v>48.35720999999999</v>
+        <v>50.0247</v>
       </c>
       <c r="G31">
         <v>0.035</v>
@@ -3818,37 +3829,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M31">
-        <v>11.402630118</v>
+        <v>11.79582426</v>
       </c>
       <c r="N31">
-        <v>-11.521130118</v>
+        <v>-11.91432426</v>
       </c>
       <c r="O31">
-        <v>-2.8802825295</v>
+        <v>-2.978581065</v>
       </c>
       <c r="P31">
-        <v>-8.640847588499998</v>
+        <v>-8.935743194999999</v>
       </c>
       <c r="Q31">
-        <v>-8.054847588499998</v>
+        <v>-8.349743194999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1316046879419234</v>
+        <v>0.1328304691982366</v>
       </c>
       <c r="T31">
-        <v>0.8297969114108154</v>
+        <v>0.8416511530023983</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.002598084800912245</v>
+        <v>-0.00251148197421517</v>
       </c>
       <c r="W31">
-        <v>0.2364126283960551</v>
+        <v>0.2363922074495199</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3856,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.0103923392036489</v>
+        <v>-0.01004592789686054</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3864,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1638989906736216</v>
+        <v>0.1657989906736216</v>
       </c>
       <c r="C32">
-        <v>35.95146022042307</v>
+        <v>32.9232237382887</v>
       </c>
       <c r="D32">
-        <v>85.94116022042307</v>
+        <v>84.5804137382887</v>
       </c>
       <c r="E32">
-        <v>49.9757</v>
+        <v>51.64319</v>
       </c>
       <c r="F32">
-        <v>50.0247</v>
+        <v>51.69219</v>
       </c>
       <c r="G32">
         <v>0.035</v>
@@ -3900,37 +3911,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M32">
-        <v>11.79582426</v>
+        <v>12.189018402</v>
       </c>
       <c r="N32">
-        <v>-11.91432426</v>
+        <v>-12.307518402</v>
       </c>
       <c r="O32">
-        <v>-2.978581065</v>
+        <v>-3.0768796005</v>
       </c>
       <c r="P32">
-        <v>-8.935743194999999</v>
+        <v>-9.2306388015</v>
       </c>
       <c r="Q32">
-        <v>-8.349743194999999</v>
+        <v>-8.644638801499999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1328304691982366</v>
+        <v>0.1340917803460371</v>
       </c>
       <c r="T32">
-        <v>0.8416511530023983</v>
+        <v>0.8538489957995345</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.00251148197421517</v>
+        <v>-0.002430466426659842</v>
       </c>
       <c r="W32">
-        <v>0.2363922074495199</v>
+        <v>0.2363731039834064</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3938,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.01004592789686054</v>
+        <v>-0.009721865706639354</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3946,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1657989906736216</v>
+        <v>0.1676989906736216</v>
       </c>
       <c r="C33">
-        <v>32.9232237382887</v>
+        <v>29.93740628360925</v>
       </c>
       <c r="D33">
-        <v>84.5804137382887</v>
+        <v>83.26208628360925</v>
       </c>
       <c r="E33">
-        <v>51.64319</v>
+        <v>53.31068</v>
       </c>
       <c r="F33">
-        <v>51.69219</v>
+        <v>53.35968</v>
       </c>
       <c r="G33">
         <v>0.035</v>
@@ -3982,37 +3993,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M33">
-        <v>12.189018402</v>
+        <v>12.582212544</v>
       </c>
       <c r="N33">
-        <v>-12.307518402</v>
+        <v>-12.700712544</v>
       </c>
       <c r="O33">
-        <v>-3.0768796005</v>
+        <v>-3.175178136</v>
       </c>
       <c r="P33">
-        <v>-9.2306388015</v>
+        <v>-9.525534407999999</v>
       </c>
       <c r="Q33">
-        <v>-8.644638801499999</v>
+        <v>-8.939534407999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1340917803460371</v>
+        <v>0.1353901888805377</v>
       </c>
       <c r="T33">
-        <v>0.8538489957995345</v>
+        <v>0.8664055986789395</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.002430466426659842</v>
+        <v>-0.002354514350826722</v>
       </c>
       <c r="W33">
-        <v>0.2363731039834064</v>
+        <v>0.236355194483925</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4020,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.009721865706639354</v>
+        <v>-0.009418057403306923</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4028,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1676989906736216</v>
+        <v>0.1695989906736216</v>
       </c>
       <c r="C34">
-        <v>29.93740628360925</v>
+        <v>26.99205478346245</v>
       </c>
       <c r="D34">
-        <v>83.26208628360925</v>
+        <v>81.98422478346245</v>
       </c>
       <c r="E34">
-        <v>53.31068</v>
+        <v>54.97817</v>
       </c>
       <c r="F34">
-        <v>53.35968</v>
+        <v>55.02717</v>
       </c>
       <c r="G34">
         <v>0.035</v>
@@ -4064,37 +4075,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M34">
-        <v>12.582212544</v>
+        <v>12.975406686</v>
       </c>
       <c r="N34">
-        <v>-12.700712544</v>
+        <v>-13.093906686</v>
       </c>
       <c r="O34">
-        <v>-3.175178136</v>
+        <v>-3.2734766715</v>
       </c>
       <c r="P34">
-        <v>-9.525534407999999</v>
+        <v>-9.820430014499999</v>
       </c>
       <c r="Q34">
-        <v>-8.939534407999998</v>
+        <v>-9.234430014499999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1353901888805377</v>
+        <v>0.1367273558787546</v>
       </c>
       <c r="T34">
-        <v>0.8664055986789395</v>
+        <v>0.8793370255248938</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.002354514350826722</v>
+        <v>-0.0022831654311047</v>
       </c>
       <c r="W34">
-        <v>0.236355194483925</v>
+        <v>0.2363383704086545</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4102,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.009418057403306923</v>
+        <v>-0.009132661724418734</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4110,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1695989906736216</v>
+        <v>0.1714989906736216</v>
       </c>
       <c r="C35">
-        <v>26.99205478346245</v>
+        <v>24.08533425142868</v>
       </c>
       <c r="D35">
-        <v>81.98422478346245</v>
+        <v>80.74499425142868</v>
       </c>
       <c r="E35">
-        <v>54.97817</v>
+        <v>56.64566</v>
       </c>
       <c r="F35">
-        <v>55.02717</v>
+        <v>56.69466</v>
       </c>
       <c r="G35">
         <v>0.035</v>
@@ -4146,37 +4157,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M35">
-        <v>12.975406686</v>
+        <v>13.368600828</v>
       </c>
       <c r="N35">
-        <v>-13.093906686</v>
+        <v>-13.487100828</v>
       </c>
       <c r="O35">
-        <v>-3.2734766715</v>
+        <v>-3.371775207</v>
       </c>
       <c r="P35">
-        <v>-9.820430014499999</v>
+        <v>-10.115325621</v>
       </c>
       <c r="Q35">
-        <v>-9.234430014499999</v>
+        <v>-9.529325621</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1367273558787546</v>
+        <v>0.1381050430890388</v>
       </c>
       <c r="T35">
-        <v>0.8793370255248938</v>
+        <v>0.8926603137904225</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.0022831654311047</v>
+        <v>-0.002216013506660444</v>
       </c>
       <c r="W35">
-        <v>0.2363383704086545</v>
+        <v>0.2363225359848705</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4184,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.009132661724418734</v>
+        <v>-0.00886405402664181</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4192,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1714989906736216</v>
+        <v>0.1733989906736216</v>
       </c>
       <c r="C36">
-        <v>24.08533425142868</v>
+        <v>21.21551899581494</v>
       </c>
       <c r="D36">
-        <v>80.74499425142868</v>
+        <v>79.54266899581495</v>
       </c>
       <c r="E36">
-        <v>56.64566</v>
+        <v>58.31315000000001</v>
       </c>
       <c r="F36">
-        <v>56.69466</v>
+        <v>58.36215000000001</v>
       </c>
       <c r="G36">
         <v>0.035</v>
@@ -4228,37 +4239,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M36">
-        <v>13.368600828</v>
+        <v>13.76179497</v>
       </c>
       <c r="N36">
-        <v>-13.487100828</v>
+        <v>-13.88029497</v>
       </c>
       <c r="O36">
-        <v>-3.371775207</v>
+        <v>-3.4700737425</v>
       </c>
       <c r="P36">
-        <v>-10.115325621</v>
+        <v>-10.4102212275</v>
       </c>
       <c r="Q36">
-        <v>-9.529325621</v>
+        <v>-9.824221227500001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1381050430890388</v>
+        <v>0.139525120675024</v>
       </c>
       <c r="T36">
-        <v>0.8926603137904225</v>
+        <v>0.9063935493871982</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.002216013506660444</v>
+        <v>-0.002152698835041574</v>
       </c>
       <c r="W36">
-        <v>0.2363225359848705</v>
+        <v>0.2363076063853028</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4266,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.00886405402664181</v>
+        <v>-0.008610795340166177</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4274,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1733989906736216</v>
+        <v>0.1752989906736216</v>
       </c>
       <c r="C37">
-        <v>21.21551899581494</v>
+        <v>18.38098460183239</v>
       </c>
       <c r="D37">
-        <v>79.54266899581495</v>
+        <v>78.3756246018324</v>
       </c>
       <c r="E37">
-        <v>58.31315000000001</v>
+        <v>59.98064000000001</v>
       </c>
       <c r="F37">
-        <v>58.36215000000001</v>
+        <v>60.02964000000001</v>
       </c>
       <c r="G37">
         <v>0.035</v>
@@ -4310,37 +4321,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M37">
-        <v>13.76179497</v>
+        <v>14.154989112</v>
       </c>
       <c r="N37">
-        <v>-13.88029497</v>
+        <v>-14.273489112</v>
       </c>
       <c r="O37">
-        <v>-3.4700737425</v>
+        <v>-3.568372278</v>
       </c>
       <c r="P37">
-        <v>-10.4102212275</v>
+        <v>-10.705116834</v>
       </c>
       <c r="Q37">
-        <v>-9.824221227500001</v>
+        <v>-10.119116834</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.139525120675024</v>
+        <v>0.1409895756855713</v>
       </c>
       <c r="T37">
-        <v>0.9063935493871982</v>
+        <v>0.9205559485963734</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.002152698835041574</v>
+        <v>-0.002092901645179308</v>
       </c>
       <c r="W37">
-        <v>0.2363076063853028</v>
+        <v>0.2362935062079333</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4348,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.008610795340166177</v>
+        <v>-0.008371606580717117</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4356,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1752989906736216</v>
+        <v>0.1771989906736216</v>
       </c>
       <c r="C38">
-        <v>18.3809846018324</v>
+        <v>15.58020060938946</v>
       </c>
       <c r="D38">
-        <v>78.3756246018324</v>
+        <v>77.24233060938946</v>
       </c>
       <c r="E38">
-        <v>59.98063999999999</v>
+        <v>61.64812999999999</v>
       </c>
       <c r="F38">
-        <v>60.02963999999999</v>
+        <v>61.69712999999999</v>
       </c>
       <c r="G38">
         <v>0.035</v>
@@ -4392,37 +4403,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M38">
-        <v>14.154989112</v>
+        <v>14.548183254</v>
       </c>
       <c r="N38">
-        <v>-14.273489112</v>
+        <v>-14.666683254</v>
       </c>
       <c r="O38">
-        <v>-3.568372278</v>
+        <v>-3.6666708135</v>
       </c>
       <c r="P38">
-        <v>-10.705116834</v>
+        <v>-11.0000124405</v>
       </c>
       <c r="Q38">
-        <v>-10.119116834</v>
+        <v>-10.4140124405</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1409895756855713</v>
+        <v>0.142500521331374</v>
       </c>
       <c r="T38">
-        <v>0.9205559485963732</v>
+        <v>0.9351679477804427</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.002092901645179309</v>
+        <v>-0.002036336735850138</v>
       </c>
       <c r="W38">
-        <v>0.2362935062079333</v>
+        <v>0.2362801682023135</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4430,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.008371606580717117</v>
+        <v>-0.008145346943400522</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4438,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1771989906736216</v>
+        <v>0.1790989906736216</v>
       </c>
       <c r="C39">
-        <v>15.58020060938946</v>
+        <v>12.81172381709501</v>
       </c>
       <c r="D39">
-        <v>77.24233060938946</v>
+        <v>76.14134381709502</v>
       </c>
       <c r="E39">
-        <v>61.64812999999999</v>
+        <v>63.31562</v>
       </c>
       <c r="F39">
-        <v>61.69712999999999</v>
+        <v>63.36462</v>
       </c>
       <c r="G39">
         <v>0.035</v>
@@ -4474,37 +4485,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M39">
-        <v>14.548183254</v>
+        <v>14.941377396</v>
       </c>
       <c r="N39">
-        <v>-14.666683254</v>
+        <v>-15.059877396</v>
       </c>
       <c r="O39">
-        <v>-3.6666708135</v>
+        <v>-3.764969349</v>
       </c>
       <c r="P39">
-        <v>-11.0000124405</v>
+        <v>-11.294908047</v>
       </c>
       <c r="Q39">
-        <v>-10.4140124405</v>
+        <v>-10.708908047</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.142500521331374</v>
+        <v>0.1440602071592993</v>
       </c>
       <c r="T39">
-        <v>0.9351679477804427</v>
+        <v>0.9502513017769013</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.002036336735850138</v>
+        <v>-0.001982748927011976</v>
       </c>
       <c r="W39">
-        <v>0.2362801682023135</v>
+        <v>0.2362675321969894</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4512,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.008145346943400522</v>
+        <v>-0.007930995708047783</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4520,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1790989906736216</v>
+        <v>0.1809989906736216</v>
       </c>
       <c r="C40">
-        <v>12.81172381709501</v>
+        <v>10.07419215086895</v>
       </c>
       <c r="D40">
-        <v>76.14134381709502</v>
+        <v>75.07130215086896</v>
       </c>
       <c r="E40">
-        <v>63.31562</v>
+        <v>64.98311</v>
       </c>
       <c r="F40">
-        <v>63.36462</v>
+        <v>65.03211</v>
       </c>
       <c r="G40">
         <v>0.035</v>
@@ -4556,37 +4567,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M40">
-        <v>14.941377396</v>
+        <v>15.334571538</v>
       </c>
       <c r="N40">
-        <v>-15.059877396</v>
+        <v>-15.453071538</v>
       </c>
       <c r="O40">
-        <v>-3.764969349</v>
+        <v>-3.8632678845</v>
       </c>
       <c r="P40">
-        <v>-11.294908047</v>
+        <v>-11.5898036535</v>
       </c>
       <c r="Q40">
-        <v>-10.708908047</v>
+        <v>-11.0038036535</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1440602071592993</v>
+        <v>0.1456710302274846</v>
       </c>
       <c r="T40">
-        <v>0.9502513017769013</v>
+        <v>0.9658291919699654</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.001982748927011976</v>
+        <v>-0.001931909210934746</v>
       </c>
       <c r="W40">
-        <v>0.2362675321969894</v>
+        <v>0.2362555441919384</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4594,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.007930995708047783</v>
+        <v>-0.007727636843738894</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4602,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1809989906736216</v>
+        <v>0.1828989906736216</v>
       </c>
       <c r="C41">
-        <v>10.07419215086895</v>
+        <v>7.366319042387815</v>
       </c>
       <c r="D41">
-        <v>75.07130215086896</v>
+        <v>74.03091904238782</v>
       </c>
       <c r="E41">
-        <v>64.98311</v>
+        <v>66.6506</v>
       </c>
       <c r="F41">
-        <v>65.03211</v>
+        <v>66.6996</v>
       </c>
       <c r="G41">
         <v>0.035</v>
@@ -4638,37 +4649,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M41">
-        <v>15.334571538</v>
+        <v>15.72776568</v>
       </c>
       <c r="N41">
-        <v>-15.453071538</v>
+        <v>-15.84626568</v>
       </c>
       <c r="O41">
-        <v>-3.8632678845</v>
+        <v>-3.96156642</v>
       </c>
       <c r="P41">
-        <v>-11.5898036535</v>
+        <v>-11.88469926</v>
       </c>
       <c r="Q41">
-        <v>-11.0038036535</v>
+        <v>-11.29869926</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1456710302274846</v>
+        <v>0.1473355473979427</v>
       </c>
       <c r="T41">
-        <v>0.9658291919699654</v>
+        <v>0.9819263451694648</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.001931909210934746</v>
+        <v>-0.001883611480661378</v>
       </c>
       <c r="W41">
-        <v>0.2362555441919384</v>
+        <v>0.2362441555871399</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4676,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.007727636843738894</v>
+        <v>-0.007534445922645405</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4684,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1828989906736216</v>
+        <v>0.1847989906736216</v>
       </c>
       <c r="C42">
-        <v>7.366319042387815</v>
+        <v>4.686888268581654</v>
       </c>
       <c r="D42">
-        <v>74.03091904238782</v>
+        <v>73.01897826858166</v>
       </c>
       <c r="E42">
-        <v>66.6506</v>
+        <v>68.31809</v>
       </c>
       <c r="F42">
-        <v>66.6996</v>
+        <v>68.36709</v>
       </c>
       <c r="G42">
         <v>0.035</v>
@@ -4720,37 +4731,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M42">
-        <v>15.72776568</v>
+        <v>16.120959822</v>
       </c>
       <c r="N42">
-        <v>-15.84626568</v>
+        <v>-16.239459822</v>
       </c>
       <c r="O42">
-        <v>-3.96156642</v>
+        <v>-4.059864955500001</v>
       </c>
       <c r="P42">
-        <v>-11.88469926</v>
+        <v>-12.1795948665</v>
       </c>
       <c r="Q42">
-        <v>-11.29869926</v>
+        <v>-11.5935948665</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1473355473979427</v>
+        <v>0.1490564888792637</v>
       </c>
       <c r="T42">
-        <v>0.9819263451694648</v>
+        <v>0.9985691645791167</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.001883611480661378</v>
+        <v>-0.001837669737230612</v>
       </c>
       <c r="W42">
-        <v>0.2362441555871399</v>
+        <v>0.236233322524039</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4758,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.007534445922645405</v>
+        <v>-0.007350678948922607</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4766,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1847989906736216</v>
+        <v>0.1866989906736216</v>
       </c>
       <c r="C43">
-        <v>4.686888268581654</v>
+        <v>2.034749208662731</v>
       </c>
       <c r="D43">
-        <v>73.01897826858166</v>
+        <v>72.03432920866274</v>
       </c>
       <c r="E43">
-        <v>68.31809</v>
+        <v>69.98558</v>
       </c>
       <c r="F43">
-        <v>68.36709</v>
+        <v>70.03458000000001</v>
       </c>
       <c r="G43">
         <v>0.035</v>
@@ -4802,37 +4813,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M43">
-        <v>16.120959822</v>
+        <v>16.514153964</v>
       </c>
       <c r="N43">
-        <v>-16.239459822</v>
+        <v>-16.632653964</v>
       </c>
       <c r="O43">
-        <v>-4.059864955500001</v>
+        <v>-4.158163491000001</v>
       </c>
       <c r="P43">
-        <v>-12.1795948665</v>
+        <v>-12.474490473</v>
       </c>
       <c r="Q43">
-        <v>-11.5935948665</v>
+        <v>-11.888490473</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1490564888792637</v>
+        <v>0.1508367731702855</v>
       </c>
       <c r="T43">
-        <v>0.9985691645791167</v>
+        <v>1.01578587431324</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.001837669737230612</v>
+        <v>-0.001793915695867979</v>
       </c>
       <c r="W43">
-        <v>0.236233322524039</v>
+        <v>0.2362230053210857</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4840,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.007350678948922607</v>
+        <v>-0.007175662783472037</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4848,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1866989906736216</v>
+        <v>0.1885989906736216</v>
       </c>
       <c r="C44">
-        <v>2.034749208662774</v>
+        <v>-0.5911875202029648</v>
       </c>
       <c r="D44">
-        <v>72.03432920866277</v>
+        <v>71.07588247979703</v>
       </c>
       <c r="E44">
-        <v>69.98557999999998</v>
+        <v>71.65306999999999</v>
       </c>
       <c r="F44">
-        <v>70.03457999999999</v>
+        <v>71.70206999999999</v>
       </c>
       <c r="G44">
         <v>0.035</v>
@@ -4884,37 +4895,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M44">
-        <v>16.514153964</v>
+        <v>16.907348106</v>
       </c>
       <c r="N44">
-        <v>-16.632653964</v>
+        <v>-17.025848106</v>
       </c>
       <c r="O44">
-        <v>-4.158163491</v>
+        <v>-4.256462026499999</v>
       </c>
       <c r="P44">
-        <v>-12.474490473</v>
+        <v>-12.7693860795</v>
       </c>
       <c r="Q44">
-        <v>-11.888490473</v>
+        <v>-12.1833860795</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1508367731702855</v>
+        <v>0.1526795235767817</v>
       </c>
       <c r="T44">
-        <v>1.015785874313239</v>
+        <v>1.033606679125752</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.001793915695867979</v>
+        <v>-0.001752196726196631</v>
       </c>
       <c r="W44">
-        <v>0.2362230053210857</v>
+        <v>0.2362131679880372</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4922,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.007175662783472037</v>
+        <v>-0.007008786904786568</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4930,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1885989906736216</v>
+        <v>0.1904989906736216</v>
       </c>
       <c r="C45">
-        <v>-0.5911875202029648</v>
+        <v>-3.191954083383791</v>
       </c>
       <c r="D45">
-        <v>71.07588247979703</v>
+        <v>70.1426059166162</v>
       </c>
       <c r="E45">
-        <v>71.65306999999999</v>
+        <v>73.32055999999999</v>
       </c>
       <c r="F45">
-        <v>71.70206999999999</v>
+        <v>73.36955999999999</v>
       </c>
       <c r="G45">
         <v>0.035</v>
@@ -4966,37 +4977,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M45">
-        <v>16.907348106</v>
+        <v>17.300542248</v>
       </c>
       <c r="N45">
-        <v>-17.025848106</v>
+        <v>-17.419042248</v>
       </c>
       <c r="O45">
-        <v>-4.256462026499999</v>
+        <v>-4.354760562</v>
       </c>
       <c r="P45">
-        <v>-12.7693860795</v>
+        <v>-13.064281686</v>
       </c>
       <c r="Q45">
-        <v>-12.1833860795</v>
+        <v>-12.478281686</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1526795235767817</v>
+        <v>0.1545880864977957</v>
       </c>
       <c r="T45">
-        <v>1.033606679125752</v>
+        <v>1.052063941252998</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.001752196726196631</v>
+        <v>-0.001712374073328525</v>
       </c>
       <c r="W45">
-        <v>0.2362131679880372</v>
+        <v>0.2362037778064908</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5004,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.007008786904786568</v>
+        <v>-0.006849496293314106</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5012,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1904989906736216</v>
+        <v>0.1923989906736216</v>
       </c>
       <c r="C46">
-        <v>-3.191954083383791</v>
+        <v>-5.768529136624565</v>
       </c>
       <c r="D46">
-        <v>70.1426059166162</v>
+        <v>69.23352086337543</v>
       </c>
       <c r="E46">
-        <v>73.32055999999999</v>
+        <v>74.98804999999999</v>
       </c>
       <c r="F46">
-        <v>73.36955999999999</v>
+        <v>75.03704999999999</v>
       </c>
       <c r="G46">
         <v>0.035</v>
@@ -5048,37 +5059,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M46">
-        <v>17.300542248</v>
+        <v>17.69373639</v>
       </c>
       <c r="N46">
-        <v>-17.419042248</v>
+        <v>-17.81223639</v>
       </c>
       <c r="O46">
-        <v>-4.354760562</v>
+        <v>-4.4530590975</v>
       </c>
       <c r="P46">
-        <v>-13.064281686</v>
+        <v>-13.3591772925</v>
       </c>
       <c r="Q46">
-        <v>-12.478281686</v>
+        <v>-12.7731772925</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1545880864977957</v>
+        <v>0.1565660517068465</v>
       </c>
       <c r="T46">
-        <v>1.052063941252998</v>
+        <v>1.071192376548507</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.001712374073328525</v>
+        <v>-0.001674321316143447</v>
       </c>
       <c r="W46">
-        <v>0.2362037778064908</v>
+        <v>0.2361948049663466</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5086,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.006849496293314106</v>
+        <v>-0.006697285264573916</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5094,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1923989906736216</v>
+        <v>0.1942989906736216</v>
       </c>
       <c r="C47">
-        <v>-5.768529136624565</v>
+        <v>-8.321841249244358</v>
       </c>
       <c r="D47">
-        <v>69.23352086337543</v>
+        <v>68.34769875075564</v>
       </c>
       <c r="E47">
-        <v>74.98804999999999</v>
+        <v>76.65553999999999</v>
       </c>
       <c r="F47">
-        <v>75.03704999999999</v>
+        <v>76.70453999999999</v>
       </c>
       <c r="G47">
         <v>0.035</v>
@@ -5130,37 +5141,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M47">
-        <v>17.69373639</v>
+        <v>18.086930532</v>
       </c>
       <c r="N47">
-        <v>-17.81223639</v>
+        <v>-18.205430532</v>
       </c>
       <c r="O47">
-        <v>-4.4530590975</v>
+        <v>-4.551357633</v>
       </c>
       <c r="P47">
-        <v>-13.3591772925</v>
+        <v>-13.654072899</v>
       </c>
       <c r="Q47">
-        <v>-12.7731772925</v>
+        <v>-13.068072899</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1565660517068465</v>
+        <v>0.158617274886603</v>
       </c>
       <c r="T47">
-        <v>1.071192376548507</v>
+        <v>1.091029272410516</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.001674321316143447</v>
+        <v>-0.001637923026662067</v>
       </c>
       <c r="W47">
-        <v>0.2361948049663466</v>
+        <v>0.2361862222496869</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5168,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.006697285264573916</v>
+        <v>-0.00655169210664841</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5176,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1942989906736216</v>
+        <v>0.1961989906736216</v>
       </c>
       <c r="C48">
-        <v>-8.321841249244358</v>
+        <v>-10.85277206786158</v>
       </c>
       <c r="D48">
-        <v>68.34769875075564</v>
+        <v>67.48425793213843</v>
       </c>
       <c r="E48">
-        <v>76.65553999999999</v>
+        <v>78.32303</v>
       </c>
       <c r="F48">
-        <v>76.70453999999999</v>
+        <v>78.37203000000001</v>
       </c>
       <c r="G48">
         <v>0.035</v>
@@ -5212,37 +5223,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M48">
-        <v>18.086930532</v>
+        <v>18.480124674</v>
       </c>
       <c r="N48">
-        <v>-18.205430532</v>
+        <v>-18.598624674</v>
       </c>
       <c r="O48">
-        <v>-4.551357633</v>
+        <v>-4.649656168500001</v>
       </c>
       <c r="P48">
-        <v>-13.654072899</v>
+        <v>-13.9489685055</v>
       </c>
       <c r="Q48">
-        <v>-13.068072899</v>
+        <v>-13.3629685055</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.158617274886603</v>
+        <v>0.1607459027146521</v>
       </c>
       <c r="T48">
-        <v>1.091029272410516</v>
+        <v>1.111614730380526</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.001637923026662067</v>
+        <v>-0.001603073600562874</v>
       </c>
       <c r="W48">
-        <v>0.2361862222496869</v>
+        <v>0.2361780047550127</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5250,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.00655169210664841</v>
+        <v>-0.00641229440225155</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5258,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1961989906736216</v>
+        <v>0.1980989906736216</v>
       </c>
       <c r="C49">
-        <v>-10.85277206786158</v>
+        <v>-13.36215924330537</v>
       </c>
       <c r="D49">
-        <v>67.48425793213843</v>
+        <v>66.64236075669464</v>
       </c>
       <c r="E49">
-        <v>78.32303</v>
+        <v>79.99052</v>
       </c>
       <c r="F49">
-        <v>78.37203000000001</v>
+        <v>80.03952000000001</v>
       </c>
       <c r="G49">
         <v>0.035</v>
@@ -5294,37 +5305,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M49">
-        <v>18.480124674</v>
+        <v>18.873318816</v>
       </c>
       <c r="N49">
-        <v>-18.598624674</v>
+        <v>-18.99181881600001</v>
       </c>
       <c r="O49">
-        <v>-4.649656168500001</v>
+        <v>-4.747954704000001</v>
       </c>
       <c r="P49">
-        <v>-13.9489685055</v>
+        <v>-14.243864112</v>
       </c>
       <c r="Q49">
-        <v>-13.3629685055</v>
+        <v>-13.657864112</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1607459027146521</v>
+        <v>0.16295640084378</v>
       </c>
       <c r="T49">
-        <v>1.111614730380526</v>
+        <v>1.132991936733998</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.001603073600562874</v>
+        <v>-0.001569676233884481</v>
       </c>
       <c r="W49">
-        <v>0.2361780047550127</v>
+        <v>0.2361701296559499</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5332,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.00641229440225155</v>
+        <v>-0.006278704935537949</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5340,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1980989906736216</v>
+        <v>0.1999989906736216</v>
       </c>
       <c r="C50">
-        <v>-13.36215924330536</v>
+        <v>-15.85079914113918</v>
       </c>
       <c r="D50">
-        <v>66.64236075669464</v>
+        <v>65.82121085886082</v>
       </c>
       <c r="E50">
-        <v>79.99051999999999</v>
+        <v>81.65800999999999</v>
       </c>
       <c r="F50">
-        <v>80.03952</v>
+        <v>81.70701</v>
       </c>
       <c r="G50">
         <v>0.035</v>
@@ -5376,37 +5387,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M50">
-        <v>18.873318816</v>
+        <v>19.266512958</v>
       </c>
       <c r="N50">
-        <v>-18.991818816</v>
+        <v>-19.385012958</v>
       </c>
       <c r="O50">
-        <v>-4.747954704000001</v>
+        <v>-4.8462532395</v>
       </c>
       <c r="P50">
-        <v>-14.243864112</v>
+        <v>-14.5387597185</v>
       </c>
       <c r="Q50">
-        <v>-13.657864112</v>
+        <v>-13.9527597185</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.16295640084378</v>
+        <v>0.1652535851740502</v>
       </c>
       <c r="T50">
-        <v>1.132991936733998</v>
+        <v>1.155207464905253</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.001569676233884481</v>
+        <v>-0.001537642025029696</v>
       </c>
       <c r="W50">
-        <v>0.2361701296559499</v>
+        <v>0.236162575989502</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5414,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.006278704935537949</v>
+        <v>-0.006150568100118825</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5422,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1999989906736216</v>
+        <v>0.2018989906736216</v>
       </c>
       <c r="C51">
-        <v>-15.85079914113918</v>
+        <v>-18.31944935423317</v>
       </c>
       <c r="D51">
-        <v>65.82121085886082</v>
+        <v>65.02005064576683</v>
       </c>
       <c r="E51">
-        <v>81.65800999999999</v>
+        <v>83.32549999999999</v>
       </c>
       <c r="F51">
-        <v>81.70701</v>
+        <v>83.3745</v>
       </c>
       <c r="G51">
         <v>0.035</v>
@@ -5458,37 +5469,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M51">
-        <v>19.266512958</v>
+        <v>19.6597071</v>
       </c>
       <c r="N51">
-        <v>-19.385012958</v>
+        <v>-19.7782071</v>
       </c>
       <c r="O51">
-        <v>-4.8462532395</v>
+        <v>-4.944551775</v>
       </c>
       <c r="P51">
-        <v>-14.5387597185</v>
+        <v>-14.833655325</v>
       </c>
       <c r="Q51">
-        <v>-13.9527597185</v>
+        <v>-14.247655325</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1652535851740502</v>
+        <v>0.1676426568775312</v>
       </c>
       <c r="T51">
-        <v>1.155207464905253</v>
+        <v>1.178311614203358</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.001537642025029696</v>
+        <v>-0.001506889184529102</v>
       </c>
       <c r="W51">
-        <v>0.236162575989502</v>
+        <v>0.236155324469712</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5496,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.006150568100118825</v>
+        <v>-0.006027556738116502</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5504,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2018989906736216</v>
+        <v>0.2037989906736216</v>
       </c>
       <c r="C52">
-        <v>-18.31944935423317</v>
+        <v>-20.7688310340487</v>
       </c>
       <c r="D52">
-        <v>65.02005064576683</v>
+        <v>64.2381589659513</v>
       </c>
       <c r="E52">
-        <v>83.32549999999999</v>
+        <v>84.99298999999999</v>
       </c>
       <c r="F52">
-        <v>83.3745</v>
+        <v>85.04199</v>
       </c>
       <c r="G52">
         <v>0.035</v>
@@ -5540,37 +5551,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M52">
-        <v>19.6597071</v>
+        <v>20.052901242</v>
       </c>
       <c r="N52">
-        <v>-19.7782071</v>
+        <v>-20.171401242</v>
       </c>
       <c r="O52">
-        <v>-4.944551775</v>
+        <v>-5.0428503105</v>
       </c>
       <c r="P52">
-        <v>-14.833655325</v>
+        <v>-15.1285509315</v>
       </c>
       <c r="Q52">
-        <v>-14.247655325</v>
+        <v>-14.5425509315</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1676426568775312</v>
+        <v>0.1701292417117666</v>
       </c>
       <c r="T52">
-        <v>1.178311614203358</v>
+        <v>1.202358790003426</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.001506889184529102</v>
+        <v>-0.001477342337773629</v>
       </c>
       <c r="W52">
-        <v>0.236155324469712</v>
+        <v>0.236148357323247</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5578,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.006027556738116502</v>
+        <v>-0.00590936935109454</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5586,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2037989906736216</v>
+        <v>0.2056989906736216</v>
       </c>
       <c r="C53">
-        <v>-20.7688310340487</v>
+        <v>-23.19963105571379</v>
       </c>
       <c r="D53">
-        <v>64.2381589659513</v>
+        <v>63.47484894428621</v>
       </c>
       <c r="E53">
-        <v>84.99298999999999</v>
+        <v>86.66047999999999</v>
       </c>
       <c r="F53">
-        <v>85.04199</v>
+        <v>86.70948</v>
       </c>
       <c r="G53">
         <v>0.035</v>
@@ -5622,37 +5633,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M53">
-        <v>20.052901242</v>
+        <v>20.446095384</v>
       </c>
       <c r="N53">
-        <v>-20.171401242</v>
+        <v>-20.564595384</v>
       </c>
       <c r="O53">
-        <v>-5.0428503105</v>
+        <v>-5.141148846</v>
       </c>
       <c r="P53">
-        <v>-15.1285509315</v>
+        <v>-15.423446538</v>
       </c>
       <c r="Q53">
-        <v>-14.5425509315</v>
+        <v>-14.837446538</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1701292417117666</v>
+        <v>0.1727194342474283</v>
       </c>
       <c r="T53">
-        <v>1.202358790003426</v>
+        <v>1.227407931461831</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.001477342337773629</v>
+        <v>-0.00144893190820106</v>
       </c>
       <c r="W53">
-        <v>0.236148357323247</v>
+        <v>0.2361416581439539</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5660,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.00590936935109454</v>
+        <v>-0.005795727632804226</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5668,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2056989906736216</v>
+        <v>0.2075989906736216</v>
       </c>
       <c r="C54">
-        <v>-23.19963105571379</v>
+        <v>-25.61250403055215</v>
       </c>
       <c r="D54">
-        <v>63.47484894428621</v>
+        <v>62.72946596944786</v>
       </c>
       <c r="E54">
-        <v>86.66047999999999</v>
+        <v>88.32796999999999</v>
       </c>
       <c r="F54">
-        <v>86.70948</v>
+        <v>88.37697</v>
       </c>
       <c r="G54">
         <v>0.035</v>
@@ -5704,37 +5715,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M54">
-        <v>20.446095384</v>
+        <v>20.839289526</v>
       </c>
       <c r="N54">
-        <v>-20.564595384</v>
+        <v>-20.957789526</v>
       </c>
       <c r="O54">
-        <v>-5.141148846</v>
+        <v>-5.239447381500001</v>
       </c>
       <c r="P54">
-        <v>-15.423446538</v>
+        <v>-15.7183421445</v>
       </c>
       <c r="Q54">
-        <v>-14.837446538</v>
+        <v>-15.1323421445</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1727194342474283</v>
+        <v>0.1754198477420545</v>
       </c>
       <c r="T54">
-        <v>1.227407931461831</v>
+        <v>1.253522993833359</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.00144893190820106</v>
+        <v>-0.001421593570310474</v>
       </c>
       <c r="W54">
-        <v>0.2361416581439539</v>
+        <v>0.2361352117638792</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5742,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.005795727632804226</v>
+        <v>-0.005686374281241857</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5750,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2075989906736216</v>
+        <v>0.2094989906736216</v>
       </c>
       <c r="C55">
-        <v>-25.61250403055215</v>
+        <v>-28.00807417845958</v>
       </c>
       <c r="D55">
-        <v>62.72946596944786</v>
+        <v>62.00138582154042</v>
       </c>
       <c r="E55">
-        <v>88.32796999999999</v>
+        <v>89.99545999999999</v>
       </c>
       <c r="F55">
-        <v>88.37697</v>
+        <v>90.04446</v>
       </c>
       <c r="G55">
         <v>0.035</v>
@@ -5786,37 +5797,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M55">
-        <v>20.839289526</v>
+        <v>21.232483668</v>
       </c>
       <c r="N55">
-        <v>-20.957789526</v>
+        <v>-21.350983668</v>
       </c>
       <c r="O55">
-        <v>-5.239447381500001</v>
+        <v>-5.337745917</v>
       </c>
       <c r="P55">
-        <v>-15.7183421445</v>
+        <v>-16.013237751</v>
       </c>
       <c r="Q55">
-        <v>-15.1323421445</v>
+        <v>-15.427237751</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1754198477420545</v>
+        <v>0.1782376705190556</v>
       </c>
       <c r="T55">
-        <v>1.253522993833359</v>
+        <v>1.280773493699302</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.001421593570310474</v>
+        <v>-0.001395267763452872</v>
       </c>
       <c r="W55">
-        <v>0.2361352117638792</v>
+        <v>0.2361290041386222</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5824,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.005686374281241857</v>
+        <v>-0.005581071053811559</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5832,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2094989906736216</v>
+        <v>0.2113989906736216</v>
       </c>
       <c r="C56">
-        <v>-28.00807417845958</v>
+        <v>-30.38693707138442</v>
       </c>
       <c r="D56">
-        <v>62.00138582154042</v>
+        <v>61.29001292861558</v>
       </c>
       <c r="E56">
-        <v>89.99545999999999</v>
+        <v>91.66295</v>
       </c>
       <c r="F56">
-        <v>90.04446</v>
+        <v>91.71195</v>
       </c>
       <c r="G56">
         <v>0.035</v>
@@ -5868,37 +5879,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M56">
-        <v>21.232483668</v>
+        <v>21.62567781</v>
       </c>
       <c r="N56">
-        <v>-21.350983668</v>
+        <v>-21.74417781</v>
       </c>
       <c r="O56">
-        <v>-5.337745917</v>
+        <v>-5.436044452500001</v>
       </c>
       <c r="P56">
-        <v>-16.013237751</v>
+        <v>-16.3081333575</v>
       </c>
       <c r="Q56">
-        <v>-15.427237751</v>
+        <v>-15.7221333575</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1782376705190556</v>
+        <v>0.1811807298639236</v>
       </c>
       <c r="T56">
-        <v>1.280773493699302</v>
+        <v>1.30923512689262</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.001395267763452872</v>
+        <v>-0.00136989925866282</v>
       </c>
       <c r="W56">
-        <v>0.2361290041386222</v>
+        <v>0.2361230222451927</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5906,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.005581071053811559</v>
+        <v>-0.005479597034651285</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5914,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2113989906736216</v>
+        <v>0.2132989906736216</v>
       </c>
       <c r="C57">
-        <v>-30.38693707138442</v>
+        <v>-32.74966125814604</v>
       </c>
       <c r="D57">
-        <v>61.29001292861558</v>
+        <v>60.59477874185396</v>
       </c>
       <c r="E57">
-        <v>91.66295</v>
+        <v>93.33044</v>
       </c>
       <c r="F57">
-        <v>91.71195</v>
+        <v>93.37944</v>
       </c>
       <c r="G57">
         <v>0.035</v>
@@ -5950,37 +5961,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M57">
-        <v>21.62567781</v>
+        <v>22.018871952</v>
       </c>
       <c r="N57">
-        <v>-21.74417781</v>
+        <v>-22.137371952</v>
       </c>
       <c r="O57">
-        <v>-5.436044452500001</v>
+        <v>-5.534342988000001</v>
       </c>
       <c r="P57">
-        <v>-16.3081333575</v>
+        <v>-16.603028964</v>
       </c>
       <c r="Q57">
-        <v>-15.7221333575</v>
+        <v>-16.017028964</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1811807298639236</v>
+        <v>0.1842575646335582</v>
       </c>
       <c r="T57">
-        <v>1.30923512689262</v>
+        <v>1.338990470685634</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.00136989925866282</v>
+        <v>-0.001345436771900984</v>
       </c>
       <c r="W57">
-        <v>0.2361230222451927</v>
+        <v>0.2361172539908143</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5988,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.005479597034651285</v>
+        <v>-0.005381747087604083</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5996,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2132989906736216</v>
+        <v>0.2151989906736216</v>
       </c>
       <c r="C58">
-        <v>-32.74966125814604</v>
+        <v>-35.0967897799088</v>
       </c>
       <c r="D58">
-        <v>60.59477874185396</v>
+        <v>59.9151402200912</v>
       </c>
       <c r="E58">
-        <v>93.33044</v>
+        <v>94.99793</v>
       </c>
       <c r="F58">
-        <v>93.37944</v>
+        <v>95.04693</v>
       </c>
       <c r="G58">
         <v>0.035</v>
@@ -6032,37 +6043,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M58">
-        <v>22.018871952</v>
+        <v>22.412066094</v>
       </c>
       <c r="N58">
-        <v>-22.137371952</v>
+        <v>-22.530566094</v>
       </c>
       <c r="O58">
-        <v>-5.534342988000001</v>
+        <v>-5.6326415235</v>
       </c>
       <c r="P58">
-        <v>-16.603028964</v>
+        <v>-16.8979245705</v>
       </c>
       <c r="Q58">
-        <v>-16.017028964</v>
+        <v>-16.3119245705</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1842575646335582</v>
+        <v>0.1874775079971293</v>
       </c>
       <c r="T58">
-        <v>1.338990470685634</v>
+        <v>1.370129783957393</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.001345436771900984</v>
+        <v>-0.001321832618007984</v>
       </c>
       <c r="W58">
-        <v>0.2361172539908143</v>
+        <v>0.2361116881313263</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6070,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.005381747087604083</v>
+        <v>-0.005287330472032004</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6078,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2151989906736216</v>
+        <v>0.2170989906736216</v>
       </c>
       <c r="C59">
-        <v>-35.0967897799088</v>
+        <v>-37.42884158480042</v>
       </c>
       <c r="D59">
-        <v>59.9151402200912</v>
+        <v>59.25057841519959</v>
       </c>
       <c r="E59">
-        <v>94.99793</v>
+        <v>96.66542</v>
       </c>
       <c r="F59">
-        <v>95.04693</v>
+        <v>96.71442</v>
       </c>
       <c r="G59">
         <v>0.035</v>
@@ -6114,37 +6125,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M59">
-        <v>22.412066094</v>
+        <v>22.805260236</v>
       </c>
       <c r="N59">
-        <v>-22.530566094</v>
+        <v>-22.923760236</v>
       </c>
       <c r="O59">
-        <v>-5.6326415235</v>
+        <v>-5.730940059000001</v>
       </c>
       <c r="P59">
-        <v>-16.8979245705</v>
+        <v>-17.192820177</v>
       </c>
       <c r="Q59">
-        <v>-16.3119245705</v>
+        <v>-16.606820177</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1874775079971293</v>
+        <v>0.190850781997061</v>
       </c>
       <c r="T59">
-        <v>1.370129783957393</v>
+        <v>1.402751921670664</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.001321832618007984</v>
+        <v>-0.001299042400456122</v>
       </c>
       <c r="W59">
-        <v>0.2361116881313263</v>
+        <v>0.2361063141980276</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6152,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.005287330472032004</v>
+        <v>-0.005196169601824563</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6160,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2170989906736216</v>
+        <v>0.2189989906736216</v>
       </c>
       <c r="C60">
-        <v>-37.42884158480039</v>
+        <v>-39.74631284941999</v>
       </c>
       <c r="D60">
-        <v>59.25057841519961</v>
+        <v>58.60059715058</v>
       </c>
       <c r="E60">
-        <v>96.66541999999998</v>
+        <v>98.33290999999998</v>
       </c>
       <c r="F60">
-        <v>96.71441999999999</v>
+        <v>98.38190999999999</v>
       </c>
       <c r="G60">
         <v>0.035</v>
@@ -6196,37 +6207,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M60">
-        <v>22.805260236</v>
+        <v>23.198454378</v>
       </c>
       <c r="N60">
-        <v>-22.923760236</v>
+        <v>-23.316954378</v>
       </c>
       <c r="O60">
-        <v>-5.730940059</v>
+        <v>-5.8292385945</v>
       </c>
       <c r="P60">
-        <v>-17.192820177</v>
+        <v>-17.4877157835</v>
       </c>
       <c r="Q60">
-        <v>-16.606820177</v>
+        <v>-16.9017157835</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.190850781997061</v>
+        <v>0.1943886059482088</v>
       </c>
       <c r="T60">
-        <v>1.402751921670664</v>
+        <v>1.436965383174826</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.001299042400456123</v>
+        <v>-0.001277024732651782</v>
       </c>
       <c r="W60">
-        <v>0.2361063141980276</v>
+        <v>0.2361011224319593</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6234,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.005196169601824563</v>
+        <v>-0.005108098930607152</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6242,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2189989906736216</v>
+        <v>0.2208989906736216</v>
       </c>
       <c r="C61">
-        <v>-39.74631284941999</v>
+        <v>-42.04967821430795</v>
       </c>
       <c r="D61">
-        <v>58.60059715058</v>
+        <v>57.96472178569204</v>
       </c>
       <c r="E61">
-        <v>98.33290999999998</v>
+        <v>100.0004</v>
       </c>
       <c r="F61">
-        <v>98.38190999999999</v>
+        <v>100.0494</v>
       </c>
       <c r="G61">
         <v>0.035</v>
@@ -6278,37 +6289,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M61">
-        <v>23.198454378</v>
+        <v>23.59164852</v>
       </c>
       <c r="N61">
-        <v>-23.316954378</v>
+        <v>-23.71014852</v>
       </c>
       <c r="O61">
-        <v>-5.8292385945</v>
+        <v>-5.92753713</v>
       </c>
       <c r="P61">
-        <v>-17.4877157835</v>
+        <v>-17.78261139</v>
       </c>
       <c r="Q61">
-        <v>-16.9017157835</v>
+        <v>-17.19661139</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1943886059482088</v>
+        <v>0.198103321096914</v>
       </c>
       <c r="T61">
-        <v>1.436965383174826</v>
+        <v>1.472889517754197</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.001277024732651782</v>
+        <v>-0.001255740987107585</v>
       </c>
       <c r="W61">
-        <v>0.2361011224319593</v>
+        <v>0.23609610372476</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6316,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.005108098930607152</v>
+        <v>-0.00502296394843027</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6324,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2208989906736216</v>
+        <v>0.2227989906736216</v>
       </c>
       <c r="C62">
-        <v>-42.04967821430795</v>
+        <v>-44.3393919398426</v>
       </c>
       <c r="D62">
-        <v>57.96472178569204</v>
+        <v>57.3424980601574</v>
       </c>
       <c r="E62">
-        <v>100.0004</v>
+        <v>101.66789</v>
       </c>
       <c r="F62">
-        <v>100.0494</v>
+        <v>101.71689</v>
       </c>
       <c r="G62">
         <v>0.035</v>
@@ -6360,37 +6371,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M62">
-        <v>23.59164852</v>
+        <v>23.984842662</v>
       </c>
       <c r="N62">
-        <v>-23.71014852</v>
+        <v>-24.103342662</v>
       </c>
       <c r="O62">
-        <v>-5.92753713</v>
+        <v>-6.0258356655</v>
       </c>
       <c r="P62">
-        <v>-17.78261139</v>
+        <v>-18.0775069965</v>
       </c>
       <c r="Q62">
-        <v>-17.19661139</v>
+        <v>-17.4915069965</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.198103321096914</v>
+        <v>0.2020085344583733</v>
       </c>
       <c r="T62">
-        <v>1.472889517754197</v>
+        <v>1.51065591564533</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.001255740987107585</v>
+        <v>-0.001235155069286149</v>
       </c>
       <c r="W62">
-        <v>0.23609610372476</v>
+        <v>0.2360912495653377</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6398,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.00502296394843027</v>
+        <v>-0.004940620277144703</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6406,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2227989906736216</v>
+        <v>0.2246989906736216</v>
       </c>
       <c r="C63">
-        <v>-44.3393919398426</v>
+        <v>-46.61588898847971</v>
       </c>
       <c r="D63">
-        <v>57.3424980601574</v>
+        <v>56.73349101152029</v>
       </c>
       <c r="E63">
-        <v>101.66789</v>
+        <v>103.33538</v>
       </c>
       <c r="F63">
-        <v>101.71689</v>
+        <v>103.38438</v>
       </c>
       <c r="G63">
         <v>0.035</v>
@@ -6442,37 +6453,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M63">
-        <v>23.984842662</v>
+        <v>24.378036804</v>
       </c>
       <c r="N63">
-        <v>-24.103342662</v>
+        <v>-24.496536804</v>
       </c>
       <c r="O63">
-        <v>-6.0258356655</v>
+        <v>-6.124134201</v>
       </c>
       <c r="P63">
-        <v>-18.0775069965</v>
+        <v>-18.372402603</v>
       </c>
       <c r="Q63">
-        <v>-17.4915069965</v>
+        <v>-17.786402603</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2020085344583733</v>
+        <v>0.2061192853651727</v>
       </c>
       <c r="T63">
-        <v>1.51065591564533</v>
+        <v>1.550410018688629</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.001235155069286149</v>
+        <v>-0.001215233213329921</v>
       </c>
       <c r="W63">
-        <v>0.2360912495653377</v>
+        <v>0.2360865519917032</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6480,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.004940620277144703</v>
+        <v>-0.004860932853319788</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6488,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2246989906736216</v>
+        <v>0.2265989906736216</v>
       </c>
       <c r="C64">
-        <v>-46.61588898847971</v>
+        <v>-48.8795860387529</v>
       </c>
       <c r="D64">
-        <v>56.73349101152029</v>
+        <v>56.13728396124709</v>
       </c>
       <c r="E64">
-        <v>103.33538</v>
+        <v>105.00287</v>
       </c>
       <c r="F64">
-        <v>103.38438</v>
+        <v>105.05187</v>
       </c>
       <c r="G64">
         <v>0.035</v>
@@ -6524,37 +6535,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M64">
-        <v>24.378036804</v>
+        <v>24.771230946</v>
       </c>
       <c r="N64">
-        <v>-24.496536804</v>
+        <v>-24.889730946</v>
       </c>
       <c r="O64">
-        <v>-6.124134201</v>
+        <v>-6.2224327365</v>
       </c>
       <c r="P64">
-        <v>-18.372402603</v>
+        <v>-18.6672982095</v>
       </c>
       <c r="Q64">
-        <v>-17.786402603</v>
+        <v>-18.0812982095</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2061192853651727</v>
+        <v>0.2104522390236908</v>
       </c>
       <c r="T64">
-        <v>1.550410018688629</v>
+        <v>1.5923129921667</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.001215233213329921</v>
+        <v>-0.001195943797245319</v>
       </c>
       <c r="W64">
-        <v>0.2360865519917032</v>
+        <v>0.2360820035473905</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6562,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.004860932853319788</v>
+        <v>-0.00478377518898121</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6570,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2265989906736216</v>
+        <v>0.2284989906736216</v>
       </c>
       <c r="C65">
-        <v>-48.8795860387529</v>
+        <v>-51.13088243600284</v>
       </c>
       <c r="D65">
-        <v>56.13728396124709</v>
+        <v>55.55347756399716</v>
       </c>
       <c r="E65">
-        <v>105.00287</v>
+        <v>106.67036</v>
       </c>
       <c r="F65">
-        <v>105.05187</v>
+        <v>106.71936</v>
       </c>
       <c r="G65">
         <v>0.035</v>
@@ -6606,37 +6617,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M65">
-        <v>24.771230946</v>
+        <v>25.164425088</v>
       </c>
       <c r="N65">
-        <v>-24.889730946</v>
+        <v>-25.282925088</v>
       </c>
       <c r="O65">
-        <v>-6.2224327365</v>
+        <v>-6.320731272</v>
       </c>
       <c r="P65">
-        <v>-18.6672982095</v>
+        <v>-18.962193816</v>
       </c>
       <c r="Q65">
-        <v>-18.0812982095</v>
+        <v>-18.376193816</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2104522390236908</v>
+        <v>0.2150259123299045</v>
       </c>
       <c r="T65">
-        <v>1.5923129921667</v>
+        <v>1.636543908615775</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.001195943797245319</v>
+        <v>-0.001177257175413361</v>
       </c>
       <c r="W65">
-        <v>0.2360820035473905</v>
+        <v>0.2360775972419625</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6644,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.00478377518898121</v>
+        <v>-0.004709028701653573</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6652,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2284989906736216</v>
+        <v>0.2303989906736216</v>
       </c>
       <c r="C66">
-        <v>-51.13088243600284</v>
+        <v>-53.37016108439377</v>
       </c>
       <c r="D66">
-        <v>55.55347756399716</v>
+        <v>54.98168891560623</v>
       </c>
       <c r="E66">
-        <v>106.67036</v>
+        <v>108.33785</v>
       </c>
       <c r="F66">
-        <v>106.71936</v>
+        <v>108.38685</v>
       </c>
       <c r="G66">
         <v>0.035</v>
@@ -6688,37 +6699,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M66">
-        <v>25.164425088</v>
+        <v>25.55761923</v>
       </c>
       <c r="N66">
-        <v>-25.282925088</v>
+        <v>-25.67611923</v>
       </c>
       <c r="O66">
-        <v>-6.320731272</v>
+        <v>-6.4190298075</v>
       </c>
       <c r="P66">
-        <v>-18.962193816</v>
+        <v>-19.2570894225</v>
       </c>
       <c r="Q66">
-        <v>-18.376193816</v>
+        <v>-18.6710894225</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2150259123299045</v>
+        <v>0.2198609383964732</v>
       </c>
       <c r="T66">
-        <v>1.636543908615775</v>
+        <v>1.683302306004797</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.001177257175413361</v>
+        <v>-0.001159145526560848</v>
       </c>
       <c r="W66">
-        <v>0.2360775972419625</v>
+        <v>0.2360733265151631</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6726,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.004709028701653573</v>
+        <v>-0.004636582106243514</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6734,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2303989906736216</v>
+        <v>0.2322989906736216</v>
       </c>
       <c r="C67">
-        <v>-53.37016108439377</v>
+        <v>-55.59778928440401</v>
       </c>
       <c r="D67">
-        <v>54.98168891560623</v>
+        <v>54.42155071559599</v>
       </c>
       <c r="E67">
-        <v>108.33785</v>
+        <v>110.00534</v>
       </c>
       <c r="F67">
-        <v>108.38685</v>
+        <v>110.05434</v>
       </c>
       <c r="G67">
         <v>0.035</v>
@@ -6770,37 +6781,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M67">
-        <v>25.55761923</v>
+        <v>25.950813372</v>
       </c>
       <c r="N67">
-        <v>-25.67611923</v>
+        <v>-26.069313372</v>
       </c>
       <c r="O67">
-        <v>-6.4190298075</v>
+        <v>-6.517328343</v>
       </c>
       <c r="P67">
-        <v>-19.2570894225</v>
+        <v>-19.551985029</v>
       </c>
       <c r="Q67">
-        <v>-18.6710894225</v>
+        <v>-18.965985029</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2198609383964732</v>
+        <v>0.2249803777610753</v>
       </c>
       <c r="T67">
-        <v>1.683302306004797</v>
+        <v>1.732811197357879</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.001159145526560848</v>
+        <v>-0.00114158271555235</v>
       </c>
       <c r="W67">
-        <v>0.2360733265151631</v>
+        <v>0.2360691852043272</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6808,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.004636582106243514</v>
+        <v>-0.004566330862209478</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6816,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2322989906736216</v>
+        <v>0.2341989906736216</v>
       </c>
       <c r="C68">
-        <v>-55.59778928440401</v>
+        <v>-57.81411951964053</v>
       </c>
       <c r="D68">
-        <v>54.42155071559599</v>
+        <v>53.87271048035947</v>
       </c>
       <c r="E68">
-        <v>110.00534</v>
+        <v>111.67283</v>
       </c>
       <c r="F68">
-        <v>110.05434</v>
+        <v>111.72183</v>
       </c>
       <c r="G68">
         <v>0.035</v>
@@ -6852,37 +6863,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M68">
-        <v>25.950813372</v>
+        <v>26.344007514</v>
       </c>
       <c r="N68">
-        <v>-26.069313372</v>
+        <v>-26.462507514</v>
       </c>
       <c r="O68">
-        <v>-6.517328343</v>
+        <v>-6.615626878500001</v>
       </c>
       <c r="P68">
-        <v>-19.551985029</v>
+        <v>-19.8468806355</v>
       </c>
       <c r="Q68">
-        <v>-18.965985029</v>
+        <v>-19.2608806355</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2249803777610753</v>
+        <v>0.2304100861780776</v>
       </c>
       <c r="T68">
-        <v>1.732811197357879</v>
+        <v>1.785320627580846</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.00114158271555235</v>
+        <v>-0.001124544167559031</v>
       </c>
       <c r="W68">
-        <v>0.2360691852043272</v>
+        <v>0.2360651675147105</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6890,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.004566330862209478</v>
+        <v>-0.004498176670236109</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6898,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2341989906736216</v>
+        <v>0.2360989906736216</v>
       </c>
       <c r="C69">
-        <v>-57.81411951964053</v>
+        <v>-60.01949019651828</v>
       </c>
       <c r="D69">
-        <v>53.87271048035947</v>
+        <v>53.33482980348172</v>
       </c>
       <c r="E69">
-        <v>111.67283</v>
+        <v>113.34032</v>
       </c>
       <c r="F69">
-        <v>111.72183</v>
+        <v>113.38932</v>
       </c>
       <c r="G69">
         <v>0.035</v>
@@ -6934,37 +6945,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M69">
-        <v>26.344007514</v>
+        <v>26.737201656</v>
       </c>
       <c r="N69">
-        <v>-26.462507514</v>
+        <v>-26.855701656</v>
       </c>
       <c r="O69">
-        <v>-6.615626878500001</v>
+        <v>-6.713925414</v>
       </c>
       <c r="P69">
-        <v>-19.8468806355</v>
+        <v>-20.141776242</v>
       </c>
       <c r="Q69">
-        <v>-19.2608806355</v>
+        <v>-19.555776242</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2304100861780776</v>
+        <v>0.2361791513711425</v>
       </c>
       <c r="T69">
-        <v>1.785320627580846</v>
+        <v>1.841111897192747</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.001124544167559031</v>
+        <v>-0.001108006753330222</v>
       </c>
       <c r="W69">
-        <v>0.2360651675147105</v>
+        <v>0.2360612679924353</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6972,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.004498176670236109</v>
+        <v>-0.004432027013320905</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6980,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2360989906736216</v>
+        <v>0.2379989906736216</v>
       </c>
       <c r="C70">
-        <v>-60.01949019651828</v>
+        <v>-62.214226340067</v>
       </c>
       <c r="D70">
-        <v>53.33482980348172</v>
+        <v>52.80758365993302</v>
       </c>
       <c r="E70">
-        <v>113.34032</v>
+        <v>115.00781</v>
       </c>
       <c r="F70">
-        <v>113.38932</v>
+        <v>115.05681</v>
       </c>
       <c r="G70">
         <v>0.035</v>
@@ -7016,37 +7027,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M70">
-        <v>26.737201656</v>
+        <v>27.13039579800001</v>
       </c>
       <c r="N70">
-        <v>-26.855701656</v>
+        <v>-27.24889579800001</v>
       </c>
       <c r="O70">
-        <v>-6.713925414</v>
+        <v>-6.812223949500002</v>
       </c>
       <c r="P70">
-        <v>-20.141776242</v>
+        <v>-20.4366718485</v>
       </c>
       <c r="Q70">
-        <v>-19.555776242</v>
+        <v>-19.85067184850001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2361791513711425</v>
+        <v>0.2423204143185988</v>
       </c>
       <c r="T70">
-        <v>1.841111897192747</v>
+        <v>1.900502603553803</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.001108006753330222</v>
+        <v>-0.001091948684441378</v>
       </c>
       <c r="W70">
-        <v>0.2360612679924353</v>
+        <v>0.2360574814997913</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7054,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.004432027013320905</v>
+        <v>-0.004367794737765607</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7062,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2379989906736216</v>
+        <v>0.2398989906736216</v>
       </c>
       <c r="C71">
-        <v>-62.214226340067</v>
+        <v>-64.39864024887075</v>
       </c>
       <c r="D71">
-        <v>52.80758365993302</v>
+        <v>52.29065975112928</v>
       </c>
       <c r="E71">
-        <v>115.00781</v>
+        <v>116.6753</v>
       </c>
       <c r="F71">
-        <v>115.05681</v>
+        <v>116.7243</v>
       </c>
       <c r="G71">
         <v>0.035</v>
@@ -7098,37 +7109,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M71">
-        <v>27.13039579800001</v>
+        <v>27.52358994</v>
       </c>
       <c r="N71">
-        <v>-27.24889579800001</v>
+        <v>-27.64208994000001</v>
       </c>
       <c r="O71">
-        <v>-6.812223949500002</v>
+        <v>-6.910522485000001</v>
       </c>
       <c r="P71">
-        <v>-20.4366718485</v>
+        <v>-20.731567455</v>
       </c>
       <c r="Q71">
-        <v>-19.85067184850001</v>
+        <v>-20.14556745500001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2423204143185988</v>
+        <v>0.2488710947958854</v>
       </c>
       <c r="T71">
-        <v>1.900502603553803</v>
+        <v>1.96385269033893</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.001091948684441378</v>
+        <v>-0.001076349417520787</v>
       </c>
       <c r="W71">
-        <v>0.2360574814997913</v>
+        <v>0.2360538031926514</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7136,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.004367794737765607</v>
+        <v>-0.004305397670083089</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7144,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2398989906736216</v>
+        <v>0.2417989906736216</v>
       </c>
       <c r="C72">
-        <v>-64.39864024887075</v>
+        <v>-66.57303211191446</v>
       </c>
       <c r="D72">
-        <v>52.29065975112928</v>
+        <v>51.78375788808556</v>
       </c>
       <c r="E72">
-        <v>116.6753</v>
+        <v>118.34279</v>
       </c>
       <c r="F72">
-        <v>116.7243</v>
+        <v>118.39179</v>
       </c>
       <c r="G72">
         <v>0.035</v>
@@ -7180,37 +7191,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M72">
-        <v>27.52358994</v>
+        <v>27.916784082</v>
       </c>
       <c r="N72">
-        <v>-27.64208994000001</v>
+        <v>-28.035284082</v>
       </c>
       <c r="O72">
-        <v>-6.910522485000001</v>
+        <v>-7.008821020500001</v>
       </c>
       <c r="P72">
-        <v>-20.731567455</v>
+        <v>-21.0264630615</v>
       </c>
       <c r="Q72">
-        <v>-20.14556745500001</v>
+        <v>-20.4404630615</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2488710947958854</v>
+        <v>0.2558735463405711</v>
       </c>
       <c r="T72">
-        <v>1.96385269033893</v>
+        <v>2.031571748626479</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.001076349417520787</v>
+        <v>-0.00106118956656979</v>
       </c>
       <c r="W72">
-        <v>0.2360538031926514</v>
+        <v>0.2360502284997971</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7218,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.004305397670083089</v>
+        <v>-0.004244758266279236</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7226,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2417989906736216</v>
+        <v>0.2436989906736216</v>
       </c>
       <c r="C73">
-        <v>-66.57303211191443</v>
+        <v>-68.73769058989635</v>
       </c>
       <c r="D73">
-        <v>51.78375788808556</v>
+        <v>51.28658941010364</v>
       </c>
       <c r="E73">
-        <v>118.34279</v>
+        <v>120.01028</v>
       </c>
       <c r="F73">
-        <v>118.39179</v>
+        <v>120.05928</v>
       </c>
       <c r="G73">
         <v>0.035</v>
@@ -7262,37 +7273,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M73">
-        <v>27.916784082</v>
+        <v>28.309978224</v>
       </c>
       <c r="N73">
-        <v>-28.035284082</v>
+        <v>-28.428478224</v>
       </c>
       <c r="O73">
-        <v>-7.0088210205</v>
+        <v>-7.107119556</v>
       </c>
       <c r="P73">
-        <v>-21.0264630615</v>
+        <v>-21.321358668</v>
       </c>
       <c r="Q73">
-        <v>-20.4404630615</v>
+        <v>-20.735358668</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.255873546340571</v>
+        <v>0.2633761729955914</v>
       </c>
       <c r="T73">
-        <v>2.031571748626479</v>
+        <v>2.104127882505995</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.00106118956656979</v>
+        <v>-0.001046450822589654</v>
       </c>
       <c r="W73">
-        <v>0.2360502284997971</v>
+        <v>0.2360467531039666</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7300,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.004244758266279236</v>
+        <v>-0.004185803290358558</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7308,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2436989906736216</v>
+        <v>0.2455989906736216</v>
       </c>
       <c r="C74">
-        <v>-68.73769058989635</v>
+        <v>-70.89289336337265</v>
       </c>
       <c r="D74">
-        <v>51.28658941010364</v>
+        <v>50.79887663662734</v>
       </c>
       <c r="E74">
-        <v>120.01028</v>
+        <v>121.67777</v>
       </c>
       <c r="F74">
-        <v>120.05928</v>
+        <v>121.72677</v>
       </c>
       <c r="G74">
         <v>0.035</v>
@@ -7344,37 +7355,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M74">
-        <v>28.309978224</v>
+        <v>28.703172366</v>
       </c>
       <c r="N74">
-        <v>-28.428478224</v>
+        <v>-28.821672366</v>
       </c>
       <c r="O74">
-        <v>-7.107119556</v>
+        <v>-7.205418091499999</v>
       </c>
       <c r="P74">
-        <v>-21.321358668</v>
+        <v>-21.6162542745</v>
       </c>
       <c r="Q74">
-        <v>-20.735358668</v>
+        <v>-21.0302542745</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2633761729955914</v>
+        <v>0.2714345497732059</v>
       </c>
       <c r="T74">
-        <v>2.104127882505995</v>
+        <v>2.182058544821033</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.001046450822589654</v>
+        <v>-0.001032115879814454</v>
       </c>
       <c r="W74">
-        <v>0.2360467531039666</v>
+        <v>0.2360433729244603</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7382,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.004185803290358558</v>
+        <v>-0.004128463519257775</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7390,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2455989906736216</v>
+        <v>0.2474989906736216</v>
       </c>
       <c r="C75">
-        <v>-70.89289336337265</v>
+        <v>-73.03890764992087</v>
       </c>
       <c r="D75">
-        <v>50.79887663662734</v>
+        <v>50.32035235007913</v>
       </c>
       <c r="E75">
-        <v>121.67777</v>
+        <v>123.34526</v>
       </c>
       <c r="F75">
-        <v>121.72677</v>
+        <v>123.39426</v>
       </c>
       <c r="G75">
         <v>0.035</v>
@@ -7426,37 +7437,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M75">
-        <v>28.703172366</v>
+        <v>29.096366508</v>
       </c>
       <c r="N75">
-        <v>-28.821672366</v>
+        <v>-29.214866508</v>
       </c>
       <c r="O75">
-        <v>-7.205418091499999</v>
+        <v>-7.303716627</v>
       </c>
       <c r="P75">
-        <v>-21.6162542745</v>
+        <v>-21.911149881</v>
       </c>
       <c r="Q75">
-        <v>-21.0302542745</v>
+        <v>-21.325149881</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2714345497732059</v>
+        <v>0.28011280168756</v>
       </c>
       <c r="T75">
-        <v>2.182058544821033</v>
+        <v>2.265983873467996</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.001032115879814454</v>
+        <v>-0.001018168367925069</v>
       </c>
       <c r="W75">
-        <v>0.2360433729244603</v>
+        <v>0.2360400841011568</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7464,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.004128463519257775</v>
+        <v>-0.004072673471700261</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7472,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2474989906736216</v>
+        <v>0.2493989906736216</v>
       </c>
       <c r="C76">
-        <v>-73.03890764992087</v>
+        <v>-75.1759906923462</v>
       </c>
       <c r="D76">
-        <v>50.32035235007913</v>
+        <v>49.8507593076538</v>
       </c>
       <c r="E76">
-        <v>123.34526</v>
+        <v>125.01275</v>
       </c>
       <c r="F76">
-        <v>123.39426</v>
+        <v>125.06175</v>
       </c>
       <c r="G76">
         <v>0.035</v>
@@ -7508,37 +7519,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M76">
-        <v>29.096366508</v>
+        <v>29.48956065</v>
       </c>
       <c r="N76">
-        <v>-29.214866508</v>
+        <v>-29.60806065</v>
       </c>
       <c r="O76">
-        <v>-7.303716627</v>
+        <v>-7.4020151625</v>
       </c>
       <c r="P76">
-        <v>-21.911149881</v>
+        <v>-22.2060454875</v>
       </c>
       <c r="Q76">
-        <v>-21.325149881</v>
+        <v>-21.6200454875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.28011280168756</v>
+        <v>0.2894853137550624</v>
       </c>
       <c r="T76">
-        <v>2.265983873467996</v>
+        <v>2.356623228406716</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.001018168367925069</v>
+        <v>-0.001004592789686068</v>
       </c>
       <c r="W76">
-        <v>0.2360400841011568</v>
+        <v>0.236036882979808</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7546,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.004072673471700261</v>
+        <v>-0.004018371158744261</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7554,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2493989906736216</v>
+        <v>0.2512989906736216</v>
       </c>
       <c r="C77">
-        <v>-75.1759906923462</v>
+        <v>-77.30439021980453</v>
       </c>
       <c r="D77">
-        <v>49.8507593076538</v>
+        <v>49.38984978019548</v>
       </c>
       <c r="E77">
-        <v>125.01275</v>
+        <v>126.68024</v>
       </c>
       <c r="F77">
-        <v>125.06175</v>
+        <v>126.72924</v>
       </c>
       <c r="G77">
         <v>0.035</v>
@@ -7590,37 +7601,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M77">
-        <v>29.48956065</v>
+        <v>29.882754792</v>
       </c>
       <c r="N77">
-        <v>-29.60806065</v>
+        <v>-30.001254792</v>
       </c>
       <c r="O77">
-        <v>-7.4020151625</v>
+        <v>-7.500313698000001</v>
       </c>
       <c r="P77">
-        <v>-22.2060454875</v>
+        <v>-22.50094109400001</v>
       </c>
       <c r="Q77">
-        <v>-21.6200454875</v>
+        <v>-21.91494109400001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2894853137550624</v>
+        <v>0.2996388684948567</v>
       </c>
       <c r="T77">
-        <v>2.356623228406716</v>
+        <v>2.454815862923662</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.001004592789686068</v>
+        <v>-0.0009913744635059881</v>
       </c>
       <c r="W77">
-        <v>0.236036882979808</v>
+        <v>0.2360337660984947</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7628,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.004018371158744261</v>
+        <v>-0.003965497854024003</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7636,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2512989906736216</v>
+        <v>0.2531989906736216</v>
       </c>
       <c r="C78">
-        <v>-77.30439021980453</v>
+        <v>-79.42434488357931</v>
       </c>
       <c r="D78">
-        <v>49.38984978019548</v>
+        <v>48.93738511642069</v>
       </c>
       <c r="E78">
-        <v>126.68024</v>
+        <v>128.34773</v>
       </c>
       <c r="F78">
-        <v>126.72924</v>
+        <v>128.39673</v>
       </c>
       <c r="G78">
         <v>0.035</v>
@@ -7672,37 +7683,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M78">
-        <v>29.882754792</v>
+        <v>30.275948934</v>
       </c>
       <c r="N78">
-        <v>-30.001254792</v>
+        <v>-30.394448934</v>
       </c>
       <c r="O78">
-        <v>-7.500313698000001</v>
+        <v>-7.5986122335</v>
       </c>
       <c r="P78">
-        <v>-22.50094109400001</v>
+        <v>-22.7958367005</v>
       </c>
       <c r="Q78">
-        <v>-21.91494109400001</v>
+        <v>-22.2098367005</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2996388684948567</v>
+        <v>0.3106753410381113</v>
       </c>
       <c r="T78">
-        <v>2.454815862923662</v>
+        <v>2.561546987398603</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.0009913744635059881</v>
+        <v>-0.0009784994704734431</v>
       </c>
       <c r="W78">
-        <v>0.2360337660984947</v>
+        <v>0.2360307301751376</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7710,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.003965497854024003</v>
+        <v>-0.003913997881893838</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7718,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2531989906736216</v>
+        <v>0.2550989906736216</v>
       </c>
       <c r="C79">
-        <v>-79.42434488357931</v>
+        <v>-81.5360846691227</v>
       </c>
       <c r="D79">
-        <v>48.93738511642069</v>
+        <v>48.49313533087731</v>
       </c>
       <c r="E79">
-        <v>128.34773</v>
+        <v>130.01522</v>
       </c>
       <c r="F79">
-        <v>128.39673</v>
+        <v>130.06422</v>
       </c>
       <c r="G79">
         <v>0.035</v>
@@ -7754,37 +7765,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M79">
-        <v>30.275948934</v>
+        <v>30.669143076</v>
       </c>
       <c r="N79">
-        <v>-30.394448934</v>
+        <v>-30.787643076</v>
       </c>
       <c r="O79">
-        <v>-7.5986122335</v>
+        <v>-7.696910769</v>
       </c>
       <c r="P79">
-        <v>-22.7958367005</v>
+        <v>-23.090732307</v>
       </c>
       <c r="Q79">
-        <v>-22.2098367005</v>
+        <v>-22.504732307</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3106753410381113</v>
+        <v>0.3227151292671164</v>
       </c>
       <c r="T79">
-        <v>2.561546987398603</v>
+        <v>2.677980941371268</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.0009784994704734431</v>
+        <v>-0.0009659546054673731</v>
       </c>
       <c r="W79">
-        <v>0.2360307301751376</v>
+        <v>0.2360277720959692</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7792,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.003913997881893838</v>
+        <v>-0.003863818421869558</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7800,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2550989906736216</v>
+        <v>0.2569989906736216</v>
       </c>
       <c r="C80">
-        <v>-81.5360846691227</v>
+        <v>-83.63983128585554</v>
       </c>
       <c r="D80">
-        <v>48.49313533087731</v>
+        <v>48.05687871414446</v>
       </c>
       <c r="E80">
-        <v>130.01522</v>
+        <v>131.68271</v>
       </c>
       <c r="F80">
-        <v>130.06422</v>
+        <v>131.73171</v>
       </c>
       <c r="G80">
         <v>0.035</v>
@@ -7836,37 +7847,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M80">
-        <v>30.669143076</v>
+        <v>31.062337218</v>
       </c>
       <c r="N80">
-        <v>-30.787643076</v>
+        <v>-31.180837218</v>
       </c>
       <c r="O80">
-        <v>-7.696910769</v>
+        <v>-7.7952093045</v>
       </c>
       <c r="P80">
-        <v>-23.090732307</v>
+        <v>-23.3856279135</v>
       </c>
       <c r="Q80">
-        <v>-22.504732307</v>
+        <v>-22.7996279135</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3227151292671164</v>
+        <v>0.335901563994122</v>
       </c>
       <c r="T80">
-        <v>2.677980941371268</v>
+        <v>2.805503843341328</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.0009659546054673731</v>
+        <v>-0.0009537273319804444</v>
       </c>
       <c r="W80">
-        <v>0.2360277720959692</v>
+        <v>0.236024888904881</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7874,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.003863818421869558</v>
+        <v>-0.003814909327921834</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7882,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2569989906736216</v>
+        <v>0.2588989906736216</v>
       </c>
       <c r="C81">
-        <v>-83.63983128585554</v>
+        <v>-85.73579853611488</v>
       </c>
       <c r="D81">
-        <v>48.05687871414446</v>
+        <v>47.62840146388513</v>
       </c>
       <c r="E81">
-        <v>131.68271</v>
+        <v>133.3502</v>
       </c>
       <c r="F81">
-        <v>131.73171</v>
+        <v>133.3992</v>
       </c>
       <c r="G81">
         <v>0.035</v>
@@ -7918,37 +7929,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M81">
-        <v>31.062337218</v>
+        <v>31.45553136</v>
       </c>
       <c r="N81">
-        <v>-31.180837218</v>
+        <v>-31.57403136</v>
       </c>
       <c r="O81">
-        <v>-7.7952093045</v>
+        <v>-7.893507840000001</v>
       </c>
       <c r="P81">
-        <v>-23.3856279135</v>
+        <v>-23.68052352</v>
       </c>
       <c r="Q81">
-        <v>-22.7996279135</v>
+        <v>-23.09452352</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.335901563994122</v>
+        <v>0.3504066421938281</v>
       </c>
       <c r="T81">
-        <v>2.805503843341328</v>
+        <v>2.945779035508395</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.0009537273319804444</v>
+        <v>-0.0009418057403306888</v>
       </c>
       <c r="W81">
-        <v>0.236024888904881</v>
+        <v>0.23602207779357</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7956,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.003814909327921834</v>
+        <v>-0.003767222961322814</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7964,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2588989906736216</v>
+        <v>0.2607989906736216</v>
       </c>
       <c r="C82">
-        <v>-85.73579853611488</v>
+        <v>-87.82419266453823</v>
       </c>
       <c r="D82">
-        <v>47.62840146388513</v>
+        <v>47.20749733546176</v>
       </c>
       <c r="E82">
-        <v>133.3502</v>
+        <v>135.01769</v>
       </c>
       <c r="F82">
-        <v>133.3992</v>
+        <v>135.06669</v>
       </c>
       <c r="G82">
         <v>0.035</v>
@@ -8000,37 +8011,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M82">
-        <v>31.45553136</v>
+        <v>31.848725502</v>
       </c>
       <c r="N82">
-        <v>-31.57403136</v>
+        <v>-31.967225502</v>
       </c>
       <c r="O82">
-        <v>-7.893507840000001</v>
+        <v>-7.9918063755</v>
       </c>
       <c r="P82">
-        <v>-23.68052352</v>
+        <v>-23.9754191265</v>
       </c>
       <c r="Q82">
-        <v>-23.09452352</v>
+        <v>-23.3894191265</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3504066421938281</v>
+        <v>0.3664385707303454</v>
       </c>
       <c r="T82">
-        <v>2.945779035508395</v>
+        <v>3.100820037377258</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.0009418057403306888</v>
+        <v>-0.0009301785089685815</v>
       </c>
       <c r="W82">
-        <v>0.23602207779357</v>
+        <v>0.2360193360924148</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8038,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.003767222961322814</v>
+        <v>-0.003720714035874373</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8046,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2607989906736216</v>
+        <v>0.2626989906736216</v>
       </c>
       <c r="C83">
-        <v>-87.82419266453823</v>
+        <v>-89.90521268908478</v>
       </c>
       <c r="D83">
-        <v>47.20749733546176</v>
+        <v>46.79396731091524</v>
       </c>
       <c r="E83">
-        <v>135.01769</v>
+        <v>136.68518</v>
       </c>
       <c r="F83">
-        <v>135.06669</v>
+        <v>136.73418</v>
       </c>
       <c r="G83">
         <v>0.035</v>
@@ -8082,37 +8093,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M83">
-        <v>31.848725502</v>
+        <v>32.24191964400001</v>
       </c>
       <c r="N83">
-        <v>-31.967225502</v>
+        <v>-32.360419644</v>
       </c>
       <c r="O83">
-        <v>-7.9918063755</v>
+        <v>-8.090104911000001</v>
       </c>
       <c r="P83">
-        <v>-23.9754191265</v>
+        <v>-24.270314733</v>
       </c>
       <c r="Q83">
-        <v>-23.3894191265</v>
+        <v>-23.684314733</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3664385707303454</v>
+        <v>0.384251824659809</v>
       </c>
       <c r="T83">
-        <v>3.100820037377258</v>
+        <v>3.27308781723155</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.0009301785089685815</v>
+        <v>-0.000918834868615306</v>
       </c>
       <c r="W83">
-        <v>0.2360193360924148</v>
+        <v>0.2360166612620195</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8120,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.003720714035874373</v>
+        <v>-0.003675339474461081</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8128,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2626989906736216</v>
+        <v>0.2645989906736216</v>
       </c>
       <c r="C84">
-        <v>-89.90521268908478</v>
+        <v>-91.97905071480925</v>
       </c>
       <c r="D84">
-        <v>46.79396731091524</v>
+        <v>46.38761928519075</v>
       </c>
       <c r="E84">
-        <v>136.68518</v>
+        <v>138.35267</v>
       </c>
       <c r="F84">
-        <v>136.73418</v>
+        <v>138.40167</v>
       </c>
       <c r="G84">
         <v>0.035</v>
@@ -8164,37 +8175,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M84">
-        <v>32.24191964400001</v>
+        <v>32.635113786</v>
       </c>
       <c r="N84">
-        <v>-32.360419644</v>
+        <v>-32.753613786</v>
       </c>
       <c r="O84">
-        <v>-8.090104911000001</v>
+        <v>-8.188403446499999</v>
       </c>
       <c r="P84">
-        <v>-24.270314733</v>
+        <v>-24.5652103395</v>
       </c>
       <c r="Q84">
-        <v>-23.684314733</v>
+        <v>-23.9792103395</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.384251824659809</v>
+        <v>0.4041607555221507</v>
       </c>
       <c r="T84">
-        <v>3.27308781723155</v>
+        <v>3.465622394715759</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.000918834868615306</v>
+        <v>-0.0009077645689934351</v>
       </c>
       <c r="W84">
-        <v>0.2360166612620195</v>
+        <v>0.2360140508853687</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8202,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.003675339474461081</v>
+        <v>-0.003631058275973764</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8210,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2645989906736216</v>
+        <v>0.2664989906736216</v>
       </c>
       <c r="C85">
-        <v>-91.97905071480925</v>
+        <v>-94.04589223142858</v>
       </c>
       <c r="D85">
-        <v>46.38761928519075</v>
+        <v>45.98826776857143</v>
       </c>
       <c r="E85">
-        <v>138.35267</v>
+        <v>140.02016</v>
       </c>
       <c r="F85">
-        <v>138.40167</v>
+        <v>140.06916</v>
       </c>
       <c r="G85">
         <v>0.035</v>
@@ -8246,37 +8257,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M85">
-        <v>32.635113786</v>
+        <v>33.028307928</v>
       </c>
       <c r="N85">
-        <v>-32.753613786</v>
+        <v>-33.146807928</v>
       </c>
       <c r="O85">
-        <v>-8.188403446499999</v>
+        <v>-8.286701982</v>
       </c>
       <c r="P85">
-        <v>-24.5652103395</v>
+        <v>-24.860105946</v>
       </c>
       <c r="Q85">
-        <v>-23.9792103395</v>
+        <v>-24.274105946</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4041607555221507</v>
+        <v>0.4265583027422853</v>
       </c>
       <c r="T85">
-        <v>3.465622394715759</v>
+        <v>3.682223794385495</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.0009077645689934351</v>
+        <v>-0.0008969578479339893</v>
       </c>
       <c r="W85">
-        <v>0.2360140508853687</v>
+        <v>0.2360115026605429</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8284,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.003631058275973764</v>
+        <v>-0.003587831391735907</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8292,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2664989906736216</v>
+        <v>0.2683989906736216</v>
       </c>
       <c r="C86">
-        <v>-94.04589223142855</v>
+        <v>-96.10591639564856</v>
       </c>
       <c r="D86">
-        <v>45.98826776857143</v>
+        <v>45.59573360435143</v>
       </c>
       <c r="E86">
-        <v>140.02016</v>
+        <v>141.68765</v>
       </c>
       <c r="F86">
-        <v>140.06916</v>
+        <v>141.73665</v>
       </c>
       <c r="G86">
         <v>0.035</v>
@@ -8328,37 +8339,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M86">
-        <v>33.028307928</v>
+        <v>33.42150207</v>
       </c>
       <c r="N86">
-        <v>-33.14680792799999</v>
+        <v>-33.54000207</v>
       </c>
       <c r="O86">
-        <v>-8.286701981999999</v>
+        <v>-8.3850005175</v>
       </c>
       <c r="P86">
-        <v>-24.860105946</v>
+        <v>-25.1550015525</v>
       </c>
       <c r="Q86">
-        <v>-24.274105946</v>
+        <v>-24.5690015525</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.426558302742285</v>
+        <v>0.4519421895917707</v>
       </c>
       <c r="T86">
-        <v>3.682223794385493</v>
+        <v>3.927705380677859</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.0008969578479339894</v>
+        <v>-0.0008864054026641777</v>
       </c>
       <c r="W86">
-        <v>0.2360115026605429</v>
+        <v>0.2360090143939483</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8366,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.003587831391735907</v>
+        <v>-0.003545621610656635</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8374,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2683989906736216</v>
+        <v>0.2702989906736216</v>
       </c>
       <c r="C87">
-        <v>-96.10591639564856</v>
+        <v>-98.15929629915468</v>
       </c>
       <c r="D87">
-        <v>45.59573360435143</v>
+        <v>45.20984370084531</v>
       </c>
       <c r="E87">
-        <v>141.68765</v>
+        <v>143.35514</v>
       </c>
       <c r="F87">
-        <v>141.73665</v>
+        <v>143.40414</v>
       </c>
       <c r="G87">
         <v>0.035</v>
@@ -8410,37 +8421,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M87">
-        <v>33.42150207</v>
+        <v>33.81469621199999</v>
       </c>
       <c r="N87">
-        <v>-33.54000207</v>
+        <v>-33.93319621199999</v>
       </c>
       <c r="O87">
-        <v>-8.3850005175</v>
+        <v>-8.483299052999998</v>
       </c>
       <c r="P87">
-        <v>-25.1550015525</v>
+        <v>-25.449897159</v>
       </c>
       <c r="Q87">
-        <v>-24.5690015525</v>
+        <v>-24.863897159</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4519421895917707</v>
+        <v>0.4809523459911828</v>
       </c>
       <c r="T87">
-        <v>3.927705380677859</v>
+        <v>4.208255765011991</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.0008864054026641777</v>
+        <v>-0.0008760983630983154</v>
       </c>
       <c r="W87">
-        <v>0.2360090143939483</v>
+        <v>0.2360065839940186</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8448,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.003545621610656635</v>
+        <v>-0.003504393452393284</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8456,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2702989906736216</v>
+        <v>0.2721989906736216</v>
       </c>
       <c r="C88">
-        <v>-98.15929629915468</v>
+        <v>-100.2061992231082</v>
       </c>
       <c r="D88">
-        <v>45.20984370084531</v>
+        <v>44.83043077689179</v>
       </c>
       <c r="E88">
-        <v>143.35514</v>
+        <v>145.02263</v>
       </c>
       <c r="F88">
-        <v>143.40414</v>
+        <v>145.07163</v>
       </c>
       <c r="G88">
         <v>0.035</v>
@@ -8492,37 +8503,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M88">
-        <v>33.81469621199999</v>
+        <v>34.207890354</v>
       </c>
       <c r="N88">
-        <v>-33.93319621199999</v>
+        <v>-34.326390354</v>
       </c>
       <c r="O88">
-        <v>-8.483299052999998</v>
+        <v>-8.581597588499999</v>
       </c>
       <c r="P88">
-        <v>-25.449897159</v>
+        <v>-25.7447927655</v>
       </c>
       <c r="Q88">
-        <v>-24.863897159</v>
+        <v>-25.1587927655</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4809523459911828</v>
+        <v>0.51442560337512</v>
       </c>
       <c r="T88">
-        <v>4.208255765011991</v>
+        <v>4.531967746935991</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.0008760983630983154</v>
+        <v>-0.0008660282669707484</v>
       </c>
       <c r="W88">
-        <v>0.2360065839940186</v>
+        <v>0.2360042094653517</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8530,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.003504393452393284</v>
+        <v>-0.003464113067882968</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8538,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2721989906736216</v>
+        <v>0.2740989906736216</v>
       </c>
       <c r="C89">
-        <v>-100.2061992231082</v>
+        <v>-102.2467868799343</v>
       </c>
       <c r="D89">
-        <v>44.83043077689179</v>
+        <v>44.45733312006567</v>
       </c>
       <c r="E89">
-        <v>145.02263</v>
+        <v>146.69012</v>
       </c>
       <c r="F89">
-        <v>145.07163</v>
+        <v>146.73912</v>
       </c>
       <c r="G89">
         <v>0.035</v>
@@ -8574,37 +8585,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M89">
-        <v>34.207890354</v>
+        <v>34.601084496</v>
       </c>
       <c r="N89">
-        <v>-34.326390354</v>
+        <v>-34.719584496</v>
       </c>
       <c r="O89">
-        <v>-8.581597588499999</v>
+        <v>-8.679896123999999</v>
       </c>
       <c r="P89">
-        <v>-25.7447927655</v>
+        <v>-26.039688372</v>
       </c>
       <c r="Q89">
-        <v>-25.1587927655</v>
+        <v>-25.453688372</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.51442560337512</v>
+        <v>0.5534777369897133</v>
       </c>
       <c r="T89">
-        <v>4.531967746935991</v>
+        <v>4.909631725847324</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.0008660282669707484</v>
+        <v>-0.0008561870366642626</v>
       </c>
       <c r="W89">
-        <v>0.2360042094653517</v>
+        <v>0.2360018889032455</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8612,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.003464113067882968</v>
+        <v>-0.003424748146656942</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8620,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2740989906736216</v>
+        <v>0.2759989906736215</v>
       </c>
       <c r="C90">
-        <v>-102.2467868799343</v>
+        <v>-104.2812156431363</v>
       </c>
       <c r="D90">
-        <v>44.45733312006567</v>
+        <v>44.09039435686369</v>
       </c>
       <c r="E90">
-        <v>146.69012</v>
+        <v>148.35761</v>
       </c>
       <c r="F90">
-        <v>146.73912</v>
+        <v>148.40661</v>
       </c>
       <c r="G90">
         <v>0.035</v>
@@ -8656,37 +8667,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M90">
-        <v>34.601084496</v>
+        <v>34.994278638</v>
       </c>
       <c r="N90">
-        <v>-34.719584496</v>
+        <v>-35.112778638</v>
       </c>
       <c r="O90">
-        <v>-8.679896123999999</v>
+        <v>-8.7781946595</v>
       </c>
       <c r="P90">
-        <v>-26.039688372</v>
+        <v>-26.3345839785</v>
       </c>
       <c r="Q90">
-        <v>-25.453688372</v>
+        <v>-25.7485839785</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5534777369897133</v>
+        <v>0.5996302585342327</v>
       </c>
       <c r="T90">
-        <v>4.909631725847324</v>
+        <v>5.355961882742535</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.0008561870366642626</v>
+        <v>-0.000846566957600619</v>
       </c>
       <c r="W90">
-        <v>0.2360018889032455</v>
+        <v>0.2359996204886022</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8694,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.003424748146656942</v>
+        <v>-0.003386267830402412</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8702,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2759989906736215</v>
+        <v>0.2778989906736216</v>
       </c>
       <c r="C91">
-        <v>-104.2812156431363</v>
+        <v>-106.309636765822</v>
       </c>
       <c r="D91">
-        <v>44.09039435686369</v>
+        <v>43.72946323417801</v>
       </c>
       <c r="E91">
-        <v>148.35761</v>
+        <v>150.0251</v>
       </c>
       <c r="F91">
-        <v>148.40661</v>
+        <v>150.0741</v>
       </c>
       <c r="G91">
         <v>0.035</v>
@@ -8738,37 +8749,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M91">
-        <v>34.994278638</v>
+        <v>35.38747278</v>
       </c>
       <c r="N91">
-        <v>-35.112778638</v>
+        <v>-35.50597277999999</v>
       </c>
       <c r="O91">
-        <v>-8.7781946595</v>
+        <v>-8.876493194999998</v>
       </c>
       <c r="P91">
-        <v>-26.3345839785</v>
+        <v>-26.629479585</v>
       </c>
       <c r="Q91">
-        <v>-25.7485839785</v>
+        <v>-26.043479585</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5996302585342327</v>
+        <v>0.655013284387656</v>
       </c>
       <c r="T91">
-        <v>5.355961882742535</v>
+        <v>5.89155807101679</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.000846566957600619</v>
+        <v>-0.0008371606580717235</v>
       </c>
       <c r="W91">
-        <v>0.2359996204886022</v>
+        <v>0.2359974024831733</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8776,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.003386267830402412</v>
+        <v>-0.003348642632286847</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8784,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2778989906736216</v>
+        <v>0.2797989906736216</v>
       </c>
       <c r="C92">
-        <v>-106.309636765822</v>
+        <v>-108.3321965885839</v>
       </c>
       <c r="D92">
-        <v>43.72946323417801</v>
+        <v>43.37439341141615</v>
       </c>
       <c r="E92">
-        <v>150.0251</v>
+        <v>151.69259</v>
       </c>
       <c r="F92">
-        <v>150.0741</v>
+        <v>151.74159</v>
       </c>
       <c r="G92">
         <v>0.035</v>
@@ -8820,37 +8831,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M92">
-        <v>35.38747278</v>
+        <v>35.780666922</v>
       </c>
       <c r="N92">
-        <v>-35.50597277999999</v>
+        <v>-35.899166922</v>
       </c>
       <c r="O92">
-        <v>-8.876493194999998</v>
+        <v>-8.9747917305</v>
       </c>
       <c r="P92">
-        <v>-26.629479585</v>
+        <v>-26.9243751915</v>
       </c>
       <c r="Q92">
-        <v>-26.043479585</v>
+        <v>-26.3383751915</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.655013284387656</v>
+        <v>0.7227036493196179</v>
       </c>
       <c r="T92">
-        <v>5.89155807101679</v>
+        <v>6.5461756344631</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.0008371606580717235</v>
+        <v>-0.0008279610904006055</v>
       </c>
       <c r="W92">
-        <v>0.2359974024831733</v>
+        <v>0.2359952332251165</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8858,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.003348642632286847</v>
+        <v>-0.003311844361602256</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8866,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2797989906736216</v>
+        <v>0.2816989906736216</v>
       </c>
       <c r="C93">
-        <v>-108.3321965885839</v>
+        <v>-110.3490367373334</v>
       </c>
       <c r="D93">
-        <v>43.37439341141615</v>
+        <v>43.02504326266664</v>
       </c>
       <c r="E93">
-        <v>151.69259</v>
+        <v>153.36008</v>
       </c>
       <c r="F93">
-        <v>151.74159</v>
+        <v>153.40908</v>
       </c>
       <c r="G93">
         <v>0.035</v>
@@ -8902,37 +8913,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M93">
-        <v>35.780666922</v>
+        <v>36.173861064</v>
       </c>
       <c r="N93">
-        <v>-35.899166922</v>
+        <v>-36.292361064</v>
       </c>
       <c r="O93">
-        <v>-8.9747917305</v>
+        <v>-9.073090265999999</v>
       </c>
       <c r="P93">
-        <v>-26.9243751915</v>
+        <v>-27.219270798</v>
       </c>
       <c r="Q93">
-        <v>-26.3383751915</v>
+        <v>-26.633270798</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7227036493196179</v>
+        <v>0.8073166054845704</v>
       </c>
       <c r="T93">
-        <v>6.5461756344631</v>
+        <v>7.364447588770989</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.0008279610904006055</v>
+        <v>-0.0008189615133310337</v>
       </c>
       <c r="W93">
-        <v>0.2359952332251165</v>
+        <v>0.2359931111248434</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8940,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.003311844361602256</v>
+        <v>-0.003275846053323983</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8948,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2816989906736216</v>
+        <v>0.2835989906736216</v>
       </c>
       <c r="C94">
-        <v>-110.3490367373334</v>
+        <v>-112.3602943116511</v>
       </c>
       <c r="D94">
-        <v>43.02504326266664</v>
+        <v>42.68127568834893</v>
       </c>
       <c r="E94">
-        <v>153.36008</v>
+        <v>155.02757</v>
       </c>
       <c r="F94">
-        <v>153.40908</v>
+        <v>155.07657</v>
       </c>
       <c r="G94">
         <v>0.035</v>
@@ -8984,37 +8995,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M94">
-        <v>36.173861064</v>
+        <v>36.567055206</v>
       </c>
       <c r="N94">
-        <v>-36.292361064</v>
+        <v>-36.685555206</v>
       </c>
       <c r="O94">
-        <v>-9.073090265999999</v>
+        <v>-9.171388801499999</v>
       </c>
       <c r="P94">
-        <v>-27.219270798</v>
+        <v>-27.5141664045</v>
       </c>
       <c r="Q94">
-        <v>-26.633270798</v>
+        <v>-26.9281664045</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8073166054845704</v>
+        <v>0.9161046919823663</v>
       </c>
       <c r="T94">
-        <v>7.364447588770989</v>
+        <v>8.416511530023989</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.0008189615133310337</v>
+        <v>-0.0008101554755532807</v>
       </c>
       <c r="W94">
-        <v>0.2359931111248434</v>
+        <v>0.2359910346611355</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9022,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.003275846053323983</v>
+        <v>-0.00324062190221297</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9030,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2835989906736216</v>
+        <v>0.2854989906736216</v>
       </c>
       <c r="C95">
-        <v>-112.3602943116511</v>
+        <v>-114.3661020641788</v>
       </c>
       <c r="D95">
-        <v>42.68127568834893</v>
+        <v>42.34295793582122</v>
       </c>
       <c r="E95">
-        <v>155.02757</v>
+        <v>156.69506</v>
       </c>
       <c r="F95">
-        <v>155.07657</v>
+        <v>156.74406</v>
       </c>
       <c r="G95">
         <v>0.035</v>
@@ -9066,37 +9077,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M95">
-        <v>36.567055206</v>
+        <v>36.960249348</v>
       </c>
       <c r="N95">
-        <v>-36.685555206</v>
+        <v>-37.078749348</v>
       </c>
       <c r="O95">
-        <v>-9.171388801499999</v>
+        <v>-9.269687337000001</v>
       </c>
       <c r="P95">
-        <v>-27.5141664045</v>
+        <v>-27.809062011</v>
       </c>
       <c r="Q95">
-        <v>-26.9281664045</v>
+        <v>-27.223062011</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9161046919823663</v>
+        <v>1.061155473979428</v>
       </c>
       <c r="T95">
-        <v>8.416511530023989</v>
+        <v>9.819263451694656</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.0008101554755532807</v>
+        <v>-0.0008015368002814372</v>
       </c>
       <c r="W95">
-        <v>0.2359910346611355</v>
+        <v>0.2359890023775064</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9104,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.00324062190221297</v>
+        <v>-0.003206147201125775</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9112,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2854989906736216</v>
+        <v>0.2873989906736216</v>
       </c>
       <c r="C96">
-        <v>-114.3661020641788</v>
+        <v>-116.3665885715473</v>
       </c>
       <c r="D96">
-        <v>42.34295793582122</v>
+        <v>42.00996142845275</v>
       </c>
       <c r="E96">
-        <v>156.69506</v>
+        <v>158.36255</v>
       </c>
       <c r="F96">
-        <v>156.74406</v>
+        <v>158.41155</v>
       </c>
       <c r="G96">
         <v>0.035</v>
@@ -9148,37 +9159,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M96">
-        <v>36.960249348</v>
+        <v>37.35344349</v>
       </c>
       <c r="N96">
-        <v>-37.078749348</v>
+        <v>-37.47194349</v>
       </c>
       <c r="O96">
-        <v>-9.269687337000001</v>
+        <v>-9.3679858725</v>
       </c>
       <c r="P96">
-        <v>-27.809062011</v>
+        <v>-28.1039576175</v>
       </c>
       <c r="Q96">
-        <v>-27.223062011</v>
+        <v>-27.5179576175</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.061155473979428</v>
+        <v>1.264226568775314</v>
       </c>
       <c r="T96">
-        <v>9.819263451694656</v>
+        <v>11.7831161420336</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.0008015368002814372</v>
+        <v>-0.0007930995708047905</v>
       </c>
       <c r="W96">
-        <v>0.2359890023775064</v>
+        <v>0.2359870128787958</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9186,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.003206147201125775</v>
+        <v>-0.003172398283219025</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9194,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2873989906736216</v>
+        <v>0.2892989906736216</v>
       </c>
       <c r="C97">
-        <v>-116.3665885715473</v>
+        <v>-118.3618783973012</v>
       </c>
       <c r="D97">
-        <v>42.00996142845275</v>
+        <v>41.68216160269888</v>
       </c>
       <c r="E97">
-        <v>158.36255</v>
+        <v>160.03004</v>
       </c>
       <c r="F97">
-        <v>158.41155</v>
+        <v>160.07904</v>
       </c>
       <c r="G97">
         <v>0.035</v>
@@ -9230,37 +9241,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M97">
-        <v>37.35344349</v>
+        <v>37.74663763200001</v>
       </c>
       <c r="N97">
-        <v>-37.47194349</v>
+        <v>-37.86513763200001</v>
       </c>
       <c r="O97">
-        <v>-9.3679858725</v>
+        <v>-9.466284408000002</v>
       </c>
       <c r="P97">
-        <v>-28.1039576175</v>
+        <v>-28.39885322400001</v>
       </c>
       <c r="Q97">
-        <v>-27.5179576175</v>
+        <v>-27.81285322400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.264226568775314</v>
+        <v>1.568833210969143</v>
       </c>
       <c r="T97">
-        <v>11.7831161420336</v>
+        <v>14.728895177542</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.0007930995708047905</v>
+        <v>-0.0007848381169422404</v>
       </c>
       <c r="W97">
-        <v>0.2359870128787958</v>
+        <v>0.235985064827975</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9268,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.003172398283219025</v>
+        <v>-0.003139352467768974</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9276,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2892989906736216</v>
+        <v>0.2911989906736216</v>
       </c>
       <c r="C98">
-        <v>-118.3618783973011</v>
+        <v>-120.3520922472556</v>
       </c>
       <c r="D98">
-        <v>41.68216160269888</v>
+        <v>41.35943775274442</v>
       </c>
       <c r="E98">
-        <v>160.03004</v>
+        <v>161.69753</v>
       </c>
       <c r="F98">
-        <v>160.07904</v>
+        <v>161.74653</v>
       </c>
       <c r="G98">
         <v>0.035</v>
@@ -9312,37 +9323,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M98">
-        <v>37.746637632</v>
+        <v>38.13983177399999</v>
       </c>
       <c r="N98">
-        <v>-37.865137632</v>
+        <v>-38.25833177399999</v>
       </c>
       <c r="O98">
-        <v>-9.466284408</v>
+        <v>-9.564582943499998</v>
       </c>
       <c r="P98">
-        <v>-28.398853224</v>
+        <v>-28.69374883049999</v>
       </c>
       <c r="Q98">
-        <v>-27.812853224</v>
+        <v>-28.10774883049999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.568833210969139</v>
+        <v>2.076510947958852</v>
       </c>
       <c r="T98">
-        <v>14.72889517754196</v>
+        <v>19.63852690338928</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.0007848381169422407</v>
+        <v>-0.0007767470023345888</v>
       </c>
       <c r="W98">
-        <v>0.235985064827975</v>
+        <v>0.2359831569431505</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9350,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.003139352467768974</v>
+        <v>-0.003106988009338396</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9358,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2911989906736216</v>
+        <v>0.2930989906736216</v>
       </c>
       <c r="C99">
-        <v>-120.3520922472556</v>
+        <v>-122.337347117691</v>
       </c>
       <c r="D99">
-        <v>41.35943775274442</v>
+        <v>41.04167288230901</v>
       </c>
       <c r="E99">
-        <v>161.69753</v>
+        <v>163.36502</v>
       </c>
       <c r="F99">
-        <v>161.74653</v>
+        <v>163.41402</v>
       </c>
       <c r="G99">
         <v>0.035</v>
@@ -9394,37 +9405,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M99">
-        <v>38.13983177399999</v>
+        <v>38.533025916</v>
       </c>
       <c r="N99">
-        <v>-38.25833177399999</v>
+        <v>-38.651525916</v>
       </c>
       <c r="O99">
-        <v>-9.564582943499998</v>
+        <v>-9.662881478999999</v>
       </c>
       <c r="P99">
-        <v>-28.69374883049999</v>
+        <v>-28.988644437</v>
       </c>
       <c r="Q99">
-        <v>-28.10774883049999</v>
+        <v>-28.402644437</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.076510947958852</v>
+        <v>3.091866421938277</v>
       </c>
       <c r="T99">
-        <v>19.63852690338928</v>
+        <v>29.45779035508392</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.0007767470023345888</v>
+        <v>-0.000768821012514848</v>
       </c>
       <c r="W99">
-        <v>0.2359831569431505</v>
+        <v>0.235981287994751</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9432,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.003106988009338396</v>
+        <v>-0.003075284050059413</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9440,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2930989906736216</v>
+        <v>0.2949989906736216</v>
       </c>
       <c r="C100">
-        <v>-122.337347117691</v>
+        <v>-124.3177564367685</v>
       </c>
       <c r="D100">
-        <v>41.04167288230901</v>
+        <v>40.72875356323151</v>
       </c>
       <c r="E100">
-        <v>163.36502</v>
+        <v>165.03251</v>
       </c>
       <c r="F100">
-        <v>163.41402</v>
+        <v>165.08151</v>
       </c>
       <c r="G100">
         <v>0.035</v>
@@ -9476,37 +9487,37 @@
         <v>-0.1185</v>
       </c>
       <c r="M100">
-        <v>38.533025916</v>
+        <v>38.926220058</v>
       </c>
       <c r="N100">
-        <v>-38.651525916</v>
+        <v>-39.044720058</v>
       </c>
       <c r="O100">
-        <v>-9.662881478999999</v>
+        <v>-9.761180014499999</v>
       </c>
       <c r="P100">
-        <v>-28.988644437</v>
+        <v>-29.2835400435</v>
       </c>
       <c r="Q100">
-        <v>-28.402644437</v>
+        <v>-28.6975400435</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.091866421938277</v>
+        <v>6.137932843876555</v>
       </c>
       <c r="T100">
-        <v>29.45779035508392</v>
+        <v>58.91558071016784</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.000768821012514848</v>
+        <v>-0.0007610551437015668</v>
       </c>
       <c r="W100">
-        <v>0.235981287994751</v>
+        <v>0.2359794568028848</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9514,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.003075284050059413</v>
+        <v>-0.003044220574806245</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2949989906736216</v>
-      </c>
-      <c r="C101">
-        <v>-124.3177564367685</v>
-      </c>
-      <c r="D101">
-        <v>40.72875356323151</v>
-      </c>
-      <c r="E101">
-        <v>165.03251</v>
-      </c>
-      <c r="F101">
-        <v>165.08151</v>
-      </c>
-      <c r="G101">
-        <v>0.035</v>
-      </c>
-      <c r="H101">
-        <v>166.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.4675</v>
-      </c>
-      <c r="K101">
-        <v>0.586</v>
-      </c>
-      <c r="L101">
-        <v>-0.1185</v>
-      </c>
-      <c r="M101">
-        <v>38.926220058</v>
-      </c>
-      <c r="N101">
-        <v>-39.044720058</v>
-      </c>
-      <c r="O101">
-        <v>-9.761180014499999</v>
-      </c>
-      <c r="P101">
-        <v>-29.2835400435</v>
-      </c>
-      <c r="Q101">
-        <v>-28.6975400435</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.137932843876555</v>
-      </c>
-      <c r="T101">
-        <v>58.91558071016784</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.0007610551437015668</v>
-      </c>
-      <c r="W101">
-        <v>0.2359794568028848</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.003044220574806245</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
